--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,8229 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120215702</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555204</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6939401</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120215730</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555499</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6939547</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120215733</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555508</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6939693</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120215668</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79511</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555394</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6939336</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120215732</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>555453</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6939688</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120215670</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555366</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6939325</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120215693</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>555255</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6939329</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120215673</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555256</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6939303</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120215712</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90067</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555317</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6939671</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120215694</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555239</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6939322</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120215711</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91886</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555311</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6939662</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>under gammal tallågerest</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120215695</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555248</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6939350</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120215725</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555442</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6939660</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120215676</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>555303</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6939259</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120215719</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555393</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6939610</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120215683</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91856</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>555323</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6939333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120215684</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>555328</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6939359</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120215729</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>555492</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6939553</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120215679</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555272</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6939241</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog på sandig getrygg</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120215674</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91024</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>555331</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6939284</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120215681</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>555310</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6939320</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120215669</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>555391</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6939341</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120215680</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>555303</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6939247</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120215726</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>555445</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6939653</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120215708</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>555296</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6939533</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120215691</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>555287</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6939378</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120215699</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91856</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>555266</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6939388</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120215724</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>555408</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6939701</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120215690</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91883</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>555293</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6939349</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120215714</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78171</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>353</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>555320</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6939663</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120215721</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>555389</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6939706</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120215741</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>555486</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6939852</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120215706</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91463</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>555195</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6939463</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120215716</v>
+      </c>
+      <c r="B48" t="n">
+        <v>89230</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>555321</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6939670</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120215731</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>555532</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6939560</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120215705</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>555220</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6939479</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120215666</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91821</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>555418</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6939343</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120215728</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>555484</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6939523</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>körspår</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120215663</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>555335</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6939295</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog på sandig getrygg</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120215727</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>555438</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6939535</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120215686</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>555296</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6939306</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120215704</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91310</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>555333</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6939465</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120215715</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91310</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>555320</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6939665</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120215743</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>555438</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6939819</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssluttning</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120215736</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>555530</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6939888</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120215662</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>555210</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6939191</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120215735</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>555516</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6939844</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssvacka</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120215722</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>555358</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6939668</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120215697</v>
+      </c>
+      <c r="B63" t="n">
+        <v>89275</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>555218</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6939369</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120215678</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>555271</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6939246</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog på sandig getrygg</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120215675</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>555371</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6939272</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120215671</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91856</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>555366</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6939325</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120215738</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>555480</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6939802</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120215665</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90399</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6020</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Oljetagging</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Sistotrema raduloides</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>555444</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6939356</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120215720</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>555385</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6939665</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120215672</v>
+      </c>
+      <c r="B70" t="n">
+        <v>90067</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>555256</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6939301</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120215703</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>555338</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6939447</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120215696</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>555200</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6939344</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120215667</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>555412</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6939333</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120215723</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91821</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>555369</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6939717</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120215677</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90067</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>555282</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6939236</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120215707</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>555227</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6939530</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120215682</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91856</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>555325</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6939312</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120215710</v>
+      </c>
+      <c r="B78" t="n">
+        <v>89230</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>555308</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6939650</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120215713</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>555307</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6939679</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120215742</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90067</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>555461</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6939822</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssluttning</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120215688</v>
+      </c>
+      <c r="B81" t="n">
+        <v>90830</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>71</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>555246</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6939300</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120215692</v>
+      </c>
+      <c r="B82" t="n">
+        <v>89275</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>555260</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6939329</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120215664</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>555450</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6939355</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120215687</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>555260</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6939288</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120215717</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>555370</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6939656</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120215740</v>
+      </c>
+      <c r="B86" t="n">
+        <v>89275</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>555485</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6939841</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120215709</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>555350</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6939568</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215702</v>
+        <v>120215710</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>89247</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,38 +2195,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555204</v>
+        <v>555308</v>
       </c>
       <c r="R15" t="n">
-        <v>6939401</v>
+        <v>6939650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215730</v>
+        <v>120215690</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,38 +2306,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555499</v>
+        <v>555293</v>
       </c>
       <c r="R16" t="n">
-        <v>6939547</v>
+        <v>6939349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215733</v>
+        <v>120215688</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>90848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,38 +2417,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555508</v>
+        <v>555246</v>
       </c>
       <c r="R17" t="n">
-        <v>6939693</v>
+        <v>6939300</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2494,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2516,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215668</v>
+        <v>120215735</v>
       </c>
       <c r="B18" t="n">
-        <v>79511</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,34 +2540,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555394</v>
+        <v>555516</v>
       </c>
       <c r="R18" t="n">
-        <v>6939336</v>
+        <v>6939844</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,15 +2613,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215732</v>
+        <v>120215722</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555453</v>
+        <v>555358</v>
       </c>
       <c r="R19" t="n">
-        <v>6939688</v>
+        <v>6939668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215670</v>
+        <v>120215728</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,14 +2782,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555366</v>
+        <v>555484</v>
       </c>
       <c r="R20" t="n">
-        <v>6939325</v>
+        <v>6939523</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2835,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215693</v>
+        <v>120215721</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,34 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555255</v>
+        <v>555389</v>
       </c>
       <c r="R21" t="n">
-        <v>6939329</v>
+        <v>6939706</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2951,15 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2968,10 +2981,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215673</v>
+        <v>120215662</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,25 +2993,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3008,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555256</v>
+        <v>555210</v>
       </c>
       <c r="R22" t="n">
-        <v>6939303</v>
+        <v>6939191</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,7 +3070,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3079,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215712</v>
+        <v>120215686</v>
       </c>
       <c r="B23" t="n">
-        <v>90067</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,34 +3108,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555317</v>
+        <v>555296</v>
       </c>
       <c r="R23" t="n">
-        <v>6939671</v>
+        <v>6939306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3181,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3190,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215694</v>
+        <v>120215743</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,14 +3239,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555239</v>
+        <v>555438</v>
       </c>
       <c r="R24" t="n">
-        <v>6939322</v>
+        <v>6939819</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3279,7 +3292,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3301,10 +3314,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215711</v>
+        <v>120215707</v>
       </c>
       <c r="B25" t="n">
-        <v>91886</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3313,25 +3326,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3341,10 +3354,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555311</v>
+        <v>555227</v>
       </c>
       <c r="R25" t="n">
-        <v>6939662</v>
+        <v>6939530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3390,12 +3403,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>under gammal tallågerest</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3417,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215695</v>
+        <v>120215674</v>
       </c>
       <c r="B26" t="n">
-        <v>91852</v>
+        <v>91042</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3429,25 +3437,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>5467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3457,10 +3465,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555248</v>
+        <v>555331</v>
       </c>
       <c r="R26" t="n">
-        <v>6939350</v>
+        <v>6939284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,7 +3514,15 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3528,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215725</v>
+        <v>120215678</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,14 +3580,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555442</v>
+        <v>555271</v>
       </c>
       <c r="R27" t="n">
-        <v>6939660</v>
+        <v>6939246</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3617,7 +3633,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3639,10 +3655,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215676</v>
+        <v>120215693</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3651,25 +3667,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3679,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555303</v>
+        <v>555255</v>
       </c>
       <c r="R28" t="n">
-        <v>6939259</v>
+        <v>6939329</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3728,7 +3744,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3750,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215719</v>
+        <v>120215711</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91904</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3762,25 +3778,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3790,10 +3806,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555393</v>
+        <v>555311</v>
       </c>
       <c r="R29" t="n">
-        <v>6939610</v>
+        <v>6939662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3839,7 +3855,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3861,10 +3882,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215683</v>
+        <v>120215717</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>78279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3877,34 +3898,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555323</v>
+        <v>555370</v>
       </c>
       <c r="R30" t="n">
-        <v>6939333</v>
+        <v>6939656</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3950,7 +3971,15 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3972,10 +4001,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215684</v>
+        <v>120215683</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3984,25 +4013,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4012,10 +4041,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555328</v>
+        <v>555323</v>
       </c>
       <c r="R31" t="n">
-        <v>6939359</v>
+        <v>6939333</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4083,10 +4112,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215729</v>
+        <v>120215727</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4095,25 +4124,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +4152,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555492</v>
+        <v>555438</v>
       </c>
       <c r="R32" t="n">
-        <v>6939553</v>
+        <v>6939535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4172,15 +4201,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4202,10 +4223,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215679</v>
+        <v>120215741</v>
       </c>
       <c r="B33" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4218,34 +4239,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555272</v>
+        <v>555486</v>
       </c>
       <c r="R33" t="n">
-        <v>6939241</v>
+        <v>6939852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4312,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4313,10 +4334,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215674</v>
+        <v>120215675</v>
       </c>
       <c r="B34" t="n">
-        <v>91024</v>
+        <v>92048</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4329,21 +4350,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5467</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4353,10 +4374,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555331</v>
+        <v>555371</v>
       </c>
       <c r="R34" t="n">
-        <v>6939284</v>
+        <v>6939272</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,7 +4423,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AN34" t="n">
@@ -4410,7 +4431,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4432,10 +4453,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215681</v>
+        <v>120215720</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4444,38 +4465,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555310</v>
+        <v>555385</v>
       </c>
       <c r="R35" t="n">
-        <v>6939320</v>
+        <v>6939665</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4521,12 +4542,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4548,10 +4564,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215669</v>
+        <v>120215694</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4588,10 +4604,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555391</v>
+        <v>555239</v>
       </c>
       <c r="R36" t="n">
-        <v>6939341</v>
+        <v>6939322</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4637,7 +4653,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4659,10 +4675,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215680</v>
+        <v>120215664</v>
       </c>
       <c r="B37" t="n">
-        <v>90527</v>
+        <v>91850</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,25 +4687,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4715,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555303</v>
+        <v>555450</v>
       </c>
       <c r="R37" t="n">
-        <v>6939247</v>
+        <v>6939355</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4748,12 +4764,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4775,10 +4786,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215726</v>
+        <v>120215716</v>
       </c>
       <c r="B38" t="n">
-        <v>91863</v>
+        <v>89247</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,25 +4798,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4826,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555445</v>
+        <v>555321</v>
       </c>
       <c r="R38" t="n">
-        <v>6939653</v>
+        <v>6939670</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4864,7 +4875,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4886,10 +4897,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215708</v>
+        <v>120215666</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91839</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4898,38 +4909,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555296</v>
+        <v>555418</v>
       </c>
       <c r="R39" t="n">
-        <v>6939533</v>
+        <v>6939343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4975,7 +4986,15 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4997,10 +5016,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215691</v>
+        <v>120215733</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5033,14 +5052,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555287</v>
+        <v>555508</v>
       </c>
       <c r="R40" t="n">
-        <v>6939378</v>
+        <v>6939693</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5086,7 +5105,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5108,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215699</v>
+        <v>120215671</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5148,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555266</v>
+        <v>555366</v>
       </c>
       <c r="R41" t="n">
-        <v>6939388</v>
+        <v>6939325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5197,7 +5216,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5219,10 +5238,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215724</v>
+        <v>120215702</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5255,14 +5274,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555408</v>
+        <v>555204</v>
       </c>
       <c r="R42" t="n">
-        <v>6939701</v>
+        <v>6939401</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5308,7 +5327,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5330,10 +5349,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215690</v>
+        <v>120215669</v>
       </c>
       <c r="B43" t="n">
-        <v>91883</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5342,25 +5361,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5370,10 +5389,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555293</v>
+        <v>555391</v>
       </c>
       <c r="R43" t="n">
-        <v>6939349</v>
+        <v>6939341</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5419,7 +5438,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5441,10 +5460,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215714</v>
+        <v>120215729</v>
       </c>
       <c r="B44" t="n">
-        <v>78171</v>
+        <v>79160</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5457,21 +5476,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5481,10 +5500,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555320</v>
+        <v>555492</v>
       </c>
       <c r="R44" t="n">
-        <v>6939663</v>
+        <v>6939553</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5530,7 +5549,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -5538,7 +5557,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5560,10 +5579,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215721</v>
+        <v>120215681</v>
       </c>
       <c r="B45" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5576,34 +5595,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555389</v>
+        <v>555310</v>
       </c>
       <c r="R45" t="n">
-        <v>6939706</v>
+        <v>6939320</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5649,15 +5668,12 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5679,10 +5695,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215741</v>
+        <v>120215677</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
+        <v>90084</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5691,38 +5707,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>256703</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555486</v>
+        <v>555282</v>
       </c>
       <c r="R46" t="n">
-        <v>6939852</v>
+        <v>6939236</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5768,7 +5784,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5790,10 +5806,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215706</v>
+        <v>120215682</v>
       </c>
       <c r="B47" t="n">
-        <v>91463</v>
+        <v>91874</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5806,34 +5822,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555195</v>
+        <v>555325</v>
       </c>
       <c r="R47" t="n">
-        <v>6939463</v>
+        <v>6939312</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5879,7 +5895,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5901,10 +5917,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120215716</v>
+        <v>120215730</v>
       </c>
       <c r="B48" t="n">
-        <v>89230</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5913,25 +5929,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5941,10 +5957,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555321</v>
+        <v>555499</v>
       </c>
       <c r="R48" t="n">
-        <v>6939670</v>
+        <v>6939547</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5990,7 +6006,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6012,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215731</v>
+        <v>120215691</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6048,14 +6064,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555532</v>
+        <v>555287</v>
       </c>
       <c r="R49" t="n">
-        <v>6939560</v>
+        <v>6939378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6101,7 +6117,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6123,10 +6139,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215705</v>
+        <v>120215738</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6159,14 +6175,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555220</v>
+        <v>555480</v>
       </c>
       <c r="R50" t="n">
-        <v>6939479</v>
+        <v>6939802</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6212,7 +6228,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6234,10 +6250,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215666</v>
+        <v>120215670</v>
       </c>
       <c r="B51" t="n">
-        <v>91821</v>
+        <v>91850</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6246,25 +6262,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6274,10 +6290,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555418</v>
+        <v>555366</v>
       </c>
       <c r="R51" t="n">
-        <v>6939343</v>
+        <v>6939325</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6323,15 +6339,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6353,10 +6361,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215728</v>
+        <v>120215668</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
+        <v>79527</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6365,38 +6373,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555484</v>
+        <v>555394</v>
       </c>
       <c r="R52" t="n">
-        <v>6939523</v>
+        <v>6939336</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6442,12 +6450,15 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN52" t="n">
+        <v>1</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>körspår</t>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6469,10 +6480,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215663</v>
+        <v>120215714</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6481,38 +6492,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555335</v>
+        <v>555320</v>
       </c>
       <c r="R53" t="n">
-        <v>6939295</v>
+        <v>6939663</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6558,7 +6569,15 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6580,10 +6599,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215727</v>
+        <v>120215667</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6592,38 +6611,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555438</v>
+        <v>555412</v>
       </c>
       <c r="R54" t="n">
-        <v>6939535</v>
+        <v>6939333</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6669,7 +6688,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6691,10 +6710,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215686</v>
+        <v>120215679</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6703,25 +6722,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6731,10 +6750,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555296</v>
+        <v>555272</v>
       </c>
       <c r="R55" t="n">
-        <v>6939306</v>
+        <v>6939241</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6780,7 +6799,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6802,10 +6821,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215704</v>
+        <v>120215708</v>
       </c>
       <c r="B56" t="n">
-        <v>91310</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6814,38 +6833,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555333</v>
+        <v>555296</v>
       </c>
       <c r="R56" t="n">
-        <v>6939465</v>
+        <v>6939533</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6891,7 +6910,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6913,10 +6932,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215715</v>
+        <v>120215740</v>
       </c>
       <c r="B57" t="n">
-        <v>91310</v>
+        <v>89292</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6929,21 +6948,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1958</v>
+        <v>6286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6953,10 +6972,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555320</v>
+        <v>555485</v>
       </c>
       <c r="R57" t="n">
-        <v>6939665</v>
+        <v>6939841</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7002,7 +7021,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7024,10 +7043,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215743</v>
+        <v>120215692</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>89292</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7036,38 +7055,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555438</v>
+        <v>555260</v>
       </c>
       <c r="R58" t="n">
-        <v>6939819</v>
+        <v>6939329</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7113,7 +7132,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7135,10 +7154,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215736</v>
+        <v>120215731</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7175,10 +7194,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555530</v>
+        <v>555532</v>
       </c>
       <c r="R59" t="n">
-        <v>6939888</v>
+        <v>6939560</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7224,7 +7243,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7246,10 +7265,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215662</v>
+        <v>120215695</v>
       </c>
       <c r="B60" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7286,10 +7305,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555210</v>
+        <v>555248</v>
       </c>
       <c r="R60" t="n">
-        <v>6939191</v>
+        <v>6939350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7335,7 +7354,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7357,10 +7376,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215735</v>
+        <v>120215699</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7369,38 +7388,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555516</v>
+        <v>555266</v>
       </c>
       <c r="R61" t="n">
-        <v>6939844</v>
+        <v>6939388</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7446,7 +7465,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7468,10 +7487,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215722</v>
+        <v>120215676</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7504,14 +7523,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555358</v>
+        <v>555303</v>
       </c>
       <c r="R62" t="n">
-        <v>6939668</v>
+        <v>6939259</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7557,7 +7576,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7579,10 +7598,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215697</v>
+        <v>120215672</v>
       </c>
       <c r="B63" t="n">
-        <v>89275</v>
+        <v>90084</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7591,25 +7610,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6286</v>
+        <v>256703</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7619,10 +7638,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555218</v>
+        <v>555256</v>
       </c>
       <c r="R63" t="n">
-        <v>6939369</v>
+        <v>6939301</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7668,7 +7687,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7690,10 +7709,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215678</v>
+        <v>120215687</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7702,25 +7721,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7730,10 +7749,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555271</v>
+        <v>555260</v>
       </c>
       <c r="R64" t="n">
-        <v>6939246</v>
+        <v>6939288</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7779,7 +7798,15 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7801,10 +7828,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215675</v>
+        <v>120215742</v>
       </c>
       <c r="B65" t="n">
-        <v>92030</v>
+        <v>90084</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7813,38 +7840,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>256703</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555371</v>
+        <v>555461</v>
       </c>
       <c r="R65" t="n">
-        <v>6939272</v>
+        <v>6939822</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7890,15 +7917,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7920,10 +7939,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215671</v>
+        <v>120215663</v>
       </c>
       <c r="B66" t="n">
-        <v>91856</v>
+        <v>91870</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7932,25 +7951,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7960,10 +7979,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555366</v>
+        <v>555335</v>
       </c>
       <c r="R66" t="n">
-        <v>6939325</v>
+        <v>6939295</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8009,7 +8028,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8031,10 +8050,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215738</v>
+        <v>120215736</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8071,10 +8090,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555480</v>
+        <v>555530</v>
       </c>
       <c r="R67" t="n">
-        <v>6939802</v>
+        <v>6939888</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8142,10 +8161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215665</v>
+        <v>120215696</v>
       </c>
       <c r="B68" t="n">
-        <v>90399</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8154,25 +8173,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6020</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8182,10 +8201,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555444</v>
+        <v>555200</v>
       </c>
       <c r="R68" t="n">
-        <v>6939356</v>
+        <v>6939344</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8231,15 +8250,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8261,10 +8272,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215720</v>
+        <v>120215709</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8301,10 +8312,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555385</v>
+        <v>555350</v>
       </c>
       <c r="R69" t="n">
-        <v>6939665</v>
+        <v>6939568</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8372,10 +8383,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215672</v>
+        <v>120215723</v>
       </c>
       <c r="B70" t="n">
-        <v>90067</v>
+        <v>91839</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8384,38 +8395,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>256703</v>
+        <v>6055</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555256</v>
+        <v>555369</v>
       </c>
       <c r="R70" t="n">
-        <v>6939301</v>
+        <v>6939717</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8461,7 +8476,15 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8483,10 +8506,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215703</v>
+        <v>120215665</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>90416</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8495,25 +8518,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6020</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8523,10 +8546,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555338</v>
+        <v>555444</v>
       </c>
       <c r="R71" t="n">
-        <v>6939447</v>
+        <v>6939356</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8572,7 +8595,15 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8594,10 +8625,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215696</v>
+        <v>120215712</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>90084</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8610,34 +8641,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555200</v>
+        <v>555317</v>
       </c>
       <c r="R72" t="n">
-        <v>6939344</v>
+        <v>6939671</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8683,7 +8714,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8705,10 +8736,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215667</v>
+        <v>120215705</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8717,25 +8748,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8745,10 +8776,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555412</v>
+        <v>555220</v>
       </c>
       <c r="R73" t="n">
-        <v>6939333</v>
+        <v>6939479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8794,7 +8825,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8816,10 +8847,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215723</v>
+        <v>120215732</v>
       </c>
       <c r="B74" t="n">
-        <v>91821</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8828,42 +8859,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555369</v>
+        <v>555453</v>
       </c>
       <c r="R74" t="n">
-        <v>6939717</v>
+        <v>6939688</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8909,15 +8936,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8939,10 +8958,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215677</v>
+        <v>120215706</v>
       </c>
       <c r="B75" t="n">
-        <v>90067</v>
+        <v>91481</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8951,38 +8970,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>256703</v>
+        <v>4745</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555282</v>
+        <v>555195</v>
       </c>
       <c r="R75" t="n">
-        <v>6939236</v>
+        <v>6939463</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,7 +9047,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9050,10 +9069,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215707</v>
+        <v>120215715</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91328</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9062,25 +9081,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9090,10 +9109,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555227</v>
+        <v>555320</v>
       </c>
       <c r="R76" t="n">
-        <v>6939530</v>
+        <v>6939665</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9139,7 +9158,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9161,10 +9180,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215682</v>
+        <v>120215684</v>
       </c>
       <c r="B77" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9173,25 +9192,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9201,10 +9220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555325</v>
+        <v>555328</v>
       </c>
       <c r="R77" t="n">
-        <v>6939312</v>
+        <v>6939359</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9272,10 +9291,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215710</v>
+        <v>120215724</v>
       </c>
       <c r="B78" t="n">
-        <v>89230</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9284,25 +9303,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9312,10 +9331,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555308</v>
+        <v>555408</v>
       </c>
       <c r="R78" t="n">
-        <v>6939650</v>
+        <v>6939701</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9361,7 +9380,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9383,10 +9402,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215713</v>
+        <v>120215703</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9419,14 +9438,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555307</v>
+        <v>555338</v>
       </c>
       <c r="R79" t="n">
-        <v>6939679</v>
+        <v>6939447</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9472,7 +9491,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9494,10 +9513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215742</v>
+        <v>120215680</v>
       </c>
       <c r="B80" t="n">
-        <v>90067</v>
+        <v>90545</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9510,34 +9529,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>256703</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555461</v>
+        <v>555303</v>
       </c>
       <c r="R80" t="n">
-        <v>6939822</v>
+        <v>6939247</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9583,7 +9602,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9605,10 +9629,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215688</v>
+        <v>120215726</v>
       </c>
       <c r="B81" t="n">
-        <v>90830</v>
+        <v>91881</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9617,38 +9641,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>71</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555246</v>
+        <v>555445</v>
       </c>
       <c r="R81" t="n">
-        <v>6939300</v>
+        <v>6939653</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9694,15 +9718,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9724,10 +9740,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215692</v>
+        <v>120215725</v>
       </c>
       <c r="B82" t="n">
-        <v>89275</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9736,38 +9752,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555260</v>
+        <v>555442</v>
       </c>
       <c r="R82" t="n">
-        <v>6939329</v>
+        <v>6939660</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9813,7 +9829,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9835,10 +9851,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215664</v>
+        <v>120215719</v>
       </c>
       <c r="B83" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9847,38 +9863,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555450</v>
+        <v>555393</v>
       </c>
       <c r="R83" t="n">
-        <v>6939355</v>
+        <v>6939610</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9924,7 +9940,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9946,10 +9962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215687</v>
+        <v>120215673</v>
       </c>
       <c r="B84" t="n">
-        <v>78263</v>
+        <v>91850</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9962,21 +9978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9986,10 +10002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555260</v>
+        <v>555256</v>
       </c>
       <c r="R84" t="n">
-        <v>6939288</v>
+        <v>6939303</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10035,15 +10051,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10065,10 +10073,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215717</v>
+        <v>120215704</v>
       </c>
       <c r="B85" t="n">
-        <v>78263</v>
+        <v>91328</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10077,38 +10085,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>1958</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555370</v>
+        <v>555333</v>
       </c>
       <c r="R85" t="n">
-        <v>6939656</v>
+        <v>6939465</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10154,15 +10162,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10184,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215740</v>
+        <v>120215697</v>
       </c>
       <c r="B86" t="n">
-        <v>89275</v>
+        <v>89292</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10220,14 +10220,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555485</v>
+        <v>555218</v>
       </c>
       <c r="R86" t="n">
-        <v>6939841</v>
+        <v>6939369</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215709</v>
+        <v>120215713</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555350</v>
+        <v>555307</v>
       </c>
       <c r="R87" t="n">
-        <v>6939568</v>
+        <v>6939679</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -3425,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215674</v>
+        <v>120215678</v>
       </c>
       <c r="B26" t="n">
-        <v>91042</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,25 +3437,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5467</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555331</v>
+        <v>555271</v>
       </c>
       <c r="R26" t="n">
-        <v>6939284</v>
+        <v>6939246</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,15 +3514,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
-        </is>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3544,10 +3536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215678</v>
+        <v>120215693</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,25 +3548,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3576,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555271</v>
+        <v>555255</v>
       </c>
       <c r="R27" t="n">
-        <v>6939246</v>
+        <v>6939329</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,7 +3625,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3655,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215693</v>
+        <v>120215674</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>91042</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3671,21 +3663,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>5467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3695,10 +3687,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555255</v>
+        <v>555331</v>
       </c>
       <c r="R28" t="n">
-        <v>6939329</v>
+        <v>6939284</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,7 +3736,15 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215727</v>
+        <v>120215741</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4124,25 +4124,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555438</v>
+        <v>555486</v>
       </c>
       <c r="R32" t="n">
-        <v>6939535</v>
+        <v>6939852</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215741</v>
+        <v>120215727</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4235,25 +4235,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555486</v>
+        <v>555438</v>
       </c>
       <c r="R33" t="n">
-        <v>6939852</v>
+        <v>6939535</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215669</v>
+        <v>120215729</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5361,38 +5361,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555391</v>
+        <v>555492</v>
       </c>
       <c r="R43" t="n">
-        <v>6939341</v>
+        <v>6939553</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5438,7 +5438,15 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5460,7 +5468,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215729</v>
+        <v>120215681</v>
       </c>
       <c r="B44" t="n">
         <v>79160</v>
@@ -5496,14 +5504,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555492</v>
+        <v>555310</v>
       </c>
       <c r="R44" t="n">
-        <v>6939553</v>
+        <v>6939320</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5549,15 +5557,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN44" t="n">
-        <v>1</v>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5579,10 +5584,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215681</v>
+        <v>120215669</v>
       </c>
       <c r="B45" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5591,25 +5596,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5619,10 +5624,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555310</v>
+        <v>555391</v>
       </c>
       <c r="R45" t="n">
-        <v>6939320</v>
+        <v>6939341</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5668,12 +5673,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215699</v>
+        <v>120215672</v>
       </c>
       <c r="B61" t="n">
-        <v>91874</v>
+        <v>90084</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7388,25 +7388,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555266</v>
+        <v>555256</v>
       </c>
       <c r="R61" t="n">
-        <v>6939388</v>
+        <v>6939301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7487,10 +7487,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215676</v>
+        <v>120215699</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7499,25 +7499,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555303</v>
+        <v>555266</v>
       </c>
       <c r="R62" t="n">
-        <v>6939259</v>
+        <v>6939388</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215672</v>
+        <v>120215676</v>
       </c>
       <c r="B63" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555256</v>
+        <v>555303</v>
       </c>
       <c r="R63" t="n">
-        <v>6939301</v>
+        <v>6939259</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215710</v>
+        <v>120215731</v>
       </c>
       <c r="B15" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555308</v>
+        <v>555532</v>
       </c>
       <c r="R15" t="n">
-        <v>6939650</v>
+        <v>6939560</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215690</v>
+        <v>120215705</v>
       </c>
       <c r="B16" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555293</v>
+        <v>555220</v>
       </c>
       <c r="R16" t="n">
-        <v>6939349</v>
+        <v>6939479</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215688</v>
+        <v>120215736</v>
       </c>
       <c r="B17" t="n">
-        <v>90848</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,38 +2417,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555246</v>
+        <v>555530</v>
       </c>
       <c r="R17" t="n">
-        <v>6939300</v>
+        <v>6939888</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,15 +2494,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2524,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215735</v>
+        <v>120215721</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2564,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555516</v>
+        <v>555389</v>
       </c>
       <c r="R18" t="n">
-        <v>6939844</v>
+        <v>6939706</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2605,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215722</v>
+        <v>120215673</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,38 +2647,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555358</v>
+        <v>555256</v>
       </c>
       <c r="R19" t="n">
-        <v>6939668</v>
+        <v>6939303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215728</v>
+        <v>120215695</v>
       </c>
       <c r="B20" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,38 +2758,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555484</v>
+        <v>555248</v>
       </c>
       <c r="R20" t="n">
-        <v>6939523</v>
+        <v>6939350</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,12 +2835,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>körspår</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2862,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215721</v>
+        <v>120215686</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,38 +2869,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555389</v>
+        <v>555296</v>
       </c>
       <c r="R21" t="n">
-        <v>6939706</v>
+        <v>6939306</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,15 +2946,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2981,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215662</v>
+        <v>120215728</v>
       </c>
       <c r="B22" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,38 +2980,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555210</v>
+        <v>555484</v>
       </c>
       <c r="R22" t="n">
-        <v>6939191</v>
+        <v>6939523</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,7 +3057,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3092,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215686</v>
+        <v>120215674</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>91042</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3104,25 +3096,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3132,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555296</v>
+        <v>555331</v>
       </c>
       <c r="R23" t="n">
-        <v>6939306</v>
+        <v>6939284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3173,15 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215743</v>
+        <v>120215741</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555438</v>
+        <v>555486</v>
       </c>
       <c r="R24" t="n">
-        <v>6939819</v>
+        <v>6939852</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215707</v>
+        <v>120215729</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,25 +3326,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555227</v>
+        <v>555492</v>
       </c>
       <c r="R25" t="n">
-        <v>6939530</v>
+        <v>6939553</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3403,15 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3425,10 +3433,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215678</v>
+        <v>120215726</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,38 +3445,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555271</v>
+        <v>555445</v>
       </c>
       <c r="R26" t="n">
-        <v>6939246</v>
+        <v>6939653</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,7 +3522,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3536,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215693</v>
+        <v>120215680</v>
       </c>
       <c r="B27" t="n">
-        <v>91850</v>
+        <v>90545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3548,25 +3556,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3576,10 +3584,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555255</v>
+        <v>555303</v>
       </c>
       <c r="R27" t="n">
-        <v>6939329</v>
+        <v>6939247</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3625,7 +3633,12 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3647,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215674</v>
+        <v>120215708</v>
       </c>
       <c r="B28" t="n">
-        <v>91042</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3659,38 +3672,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5467</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555331</v>
+        <v>555296</v>
       </c>
       <c r="R28" t="n">
-        <v>6939284</v>
+        <v>6939533</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3736,15 +3749,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
-        </is>
-      </c>
-      <c r="AN28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3766,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215711</v>
+        <v>120215707</v>
       </c>
       <c r="B29" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3778,25 +3783,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3806,10 +3811,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555311</v>
+        <v>555227</v>
       </c>
       <c r="R29" t="n">
-        <v>6939662</v>
+        <v>6939530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,12 +3860,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>under gammal tallågerest</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215717</v>
+        <v>120215679</v>
       </c>
       <c r="B30" t="n">
-        <v>78279</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555370</v>
+        <v>555272</v>
       </c>
       <c r="R30" t="n">
-        <v>6939656</v>
+        <v>6939241</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3971,15 +3971,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4001,10 +3993,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215683</v>
+        <v>120215678</v>
       </c>
       <c r="B31" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4013,25 +4005,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4041,10 +4033,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555323</v>
+        <v>555271</v>
       </c>
       <c r="R31" t="n">
-        <v>6939333</v>
+        <v>6939246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4090,7 +4082,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4112,10 +4104,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215741</v>
+        <v>120215732</v>
       </c>
       <c r="B32" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4124,25 +4116,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4152,10 +4144,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555486</v>
+        <v>555453</v>
       </c>
       <c r="R32" t="n">
-        <v>6939852</v>
+        <v>6939688</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4201,7 +4193,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4223,10 +4215,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215727</v>
+        <v>120215671</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4235,38 +4227,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555438</v>
+        <v>555366</v>
       </c>
       <c r="R33" t="n">
-        <v>6939535</v>
+        <v>6939325</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4312,7 +4304,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4334,10 +4326,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215675</v>
+        <v>120215668</v>
       </c>
       <c r="B34" t="n">
-        <v>92048</v>
+        <v>79527</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,25 +4338,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4374,10 +4366,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555371</v>
+        <v>555394</v>
       </c>
       <c r="R34" t="n">
-        <v>6939272</v>
+        <v>6939336</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4431,7 +4423,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4453,10 +4445,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215720</v>
+        <v>120215682</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4465,38 +4457,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555385</v>
+        <v>555325</v>
       </c>
       <c r="R35" t="n">
-        <v>6939665</v>
+        <v>6939312</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4542,7 +4534,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4564,10 +4556,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215694</v>
+        <v>120215712</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4580,34 +4572,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555239</v>
+        <v>555317</v>
       </c>
       <c r="R36" t="n">
-        <v>6939322</v>
+        <v>6939671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4653,7 +4645,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4675,10 +4667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215664</v>
+        <v>120215742</v>
       </c>
       <c r="B37" t="n">
-        <v>91850</v>
+        <v>90084</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4687,38 +4679,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>256703</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555450</v>
+        <v>555461</v>
       </c>
       <c r="R37" t="n">
-        <v>6939355</v>
+        <v>6939822</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4764,7 +4756,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4786,10 +4778,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215716</v>
+        <v>120215688</v>
       </c>
       <c r="B38" t="n">
-        <v>89247</v>
+        <v>90848</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4798,38 +4790,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1596</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555321</v>
+        <v>555246</v>
       </c>
       <c r="R38" t="n">
-        <v>6939670</v>
+        <v>6939300</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4875,7 +4867,15 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215666</v>
+        <v>120215670</v>
       </c>
       <c r="B39" t="n">
-        <v>91839</v>
+        <v>91850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4909,25 +4909,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555418</v>
+        <v>555366</v>
       </c>
       <c r="R39" t="n">
-        <v>6939343</v>
+        <v>6939325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4986,15 +4986,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5016,7 +5008,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215733</v>
+        <v>120215694</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5052,14 +5044,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555508</v>
+        <v>555239</v>
       </c>
       <c r="R40" t="n">
-        <v>6939693</v>
+        <v>6939322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5105,7 +5097,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5127,10 +5119,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215671</v>
+        <v>120215667</v>
       </c>
       <c r="B41" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5143,21 +5135,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5159,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555366</v>
+        <v>555412</v>
       </c>
       <c r="R41" t="n">
-        <v>6939325</v>
+        <v>6939333</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5216,7 +5208,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5349,10 +5341,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215729</v>
+        <v>120215727</v>
       </c>
       <c r="B43" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5361,25 +5353,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5389,10 +5381,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555492</v>
+        <v>555438</v>
       </c>
       <c r="R43" t="n">
-        <v>6939553</v>
+        <v>6939535</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5438,15 +5430,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5468,10 +5452,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215681</v>
+        <v>120215703</v>
       </c>
       <c r="B44" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5480,25 +5464,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5508,10 +5492,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555310</v>
+        <v>555338</v>
       </c>
       <c r="R44" t="n">
-        <v>6939320</v>
+        <v>6939447</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,12 +5541,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5584,10 +5563,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215669</v>
+        <v>120215704</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5596,25 +5575,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5624,10 +5603,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555391</v>
+        <v>555333</v>
       </c>
       <c r="R45" t="n">
-        <v>6939341</v>
+        <v>6939465</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5673,7 +5652,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5695,10 +5674,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215677</v>
+        <v>120215684</v>
       </c>
       <c r="B46" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5711,21 +5690,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5735,10 +5714,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555282</v>
+        <v>555328</v>
       </c>
       <c r="R46" t="n">
-        <v>6939236</v>
+        <v>6939359</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5784,7 +5763,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5806,10 +5785,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215682</v>
+        <v>120215663</v>
       </c>
       <c r="B47" t="n">
-        <v>91874</v>
+        <v>91870</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,25 +5797,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5846,10 +5825,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555325</v>
+        <v>555335</v>
       </c>
       <c r="R47" t="n">
-        <v>6939312</v>
+        <v>6939295</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5895,7 +5874,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6028,7 +6007,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215691</v>
+        <v>120215722</v>
       </c>
       <c r="B49" t="n">
         <v>91858</v>
@@ -6064,14 +6043,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555287</v>
+        <v>555358</v>
       </c>
       <c r="R49" t="n">
-        <v>6939378</v>
+        <v>6939668</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6117,7 +6096,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6139,7 +6118,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215738</v>
+        <v>120215696</v>
       </c>
       <c r="B50" t="n">
         <v>91858</v>
@@ -6175,14 +6154,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555480</v>
+        <v>555200</v>
       </c>
       <c r="R50" t="n">
-        <v>6939802</v>
+        <v>6939344</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6228,7 +6207,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6250,10 +6229,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215670</v>
+        <v>120215690</v>
       </c>
       <c r="B51" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6266,21 +6245,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6290,10 +6269,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555366</v>
+        <v>555293</v>
       </c>
       <c r="R51" t="n">
-        <v>6939325</v>
+        <v>6939349</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6339,7 +6318,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6361,10 +6340,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215668</v>
+        <v>120215665</v>
       </c>
       <c r="B52" t="n">
-        <v>79527</v>
+        <v>90416</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6373,25 +6352,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6020</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6401,10 +6380,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555394</v>
+        <v>555444</v>
       </c>
       <c r="R52" t="n">
-        <v>6939336</v>
+        <v>6939356</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6450,7 +6429,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AN52" t="n">
@@ -6458,7 +6437,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6480,10 +6459,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215714</v>
+        <v>120215716</v>
       </c>
       <c r="B53" t="n">
-        <v>78187</v>
+        <v>89247</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6492,25 +6471,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>1596</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6520,10 +6499,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555320</v>
+        <v>555321</v>
       </c>
       <c r="R53" t="n">
-        <v>6939663</v>
+        <v>6939670</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6570,14 +6549,6 @@
       <c r="AI53" t="inlineStr">
         <is>
           <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6599,10 +6570,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215667</v>
+        <v>120215714</v>
       </c>
       <c r="B54" t="n">
-        <v>91850</v>
+        <v>78187</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6615,34 +6586,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555412</v>
+        <v>555320</v>
       </c>
       <c r="R54" t="n">
-        <v>6939333</v>
+        <v>6939663</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6688,7 +6659,15 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6710,10 +6689,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215679</v>
+        <v>120215697</v>
       </c>
       <c r="B55" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6722,25 +6701,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6750,10 +6729,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555272</v>
+        <v>555218</v>
       </c>
       <c r="R55" t="n">
-        <v>6939241</v>
+        <v>6939369</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6799,7 +6778,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6821,10 +6800,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215708</v>
+        <v>120215692</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6833,38 +6812,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555296</v>
+        <v>555260</v>
       </c>
       <c r="R56" t="n">
-        <v>6939533</v>
+        <v>6939329</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6910,7 +6889,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6932,10 +6911,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215740</v>
+        <v>120215725</v>
       </c>
       <c r="B57" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6944,25 +6923,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6972,10 +6951,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555485</v>
+        <v>555442</v>
       </c>
       <c r="R57" t="n">
-        <v>6939841</v>
+        <v>6939660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7021,7 +7000,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7043,10 +7022,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215692</v>
+        <v>120215710</v>
       </c>
       <c r="B58" t="n">
-        <v>89292</v>
+        <v>89247</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7059,16 +7038,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6286</v>
+        <v>1596</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7079,14 +7058,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555260</v>
+        <v>555308</v>
       </c>
       <c r="R58" t="n">
-        <v>6939329</v>
+        <v>6939650</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7132,7 +7111,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7154,10 +7133,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215731</v>
+        <v>120215687</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7166,38 +7145,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555532</v>
+        <v>555260</v>
       </c>
       <c r="R59" t="n">
-        <v>6939560</v>
+        <v>6939288</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7243,7 +7222,15 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7265,10 +7252,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215695</v>
+        <v>120215717</v>
       </c>
       <c r="B60" t="n">
-        <v>91870</v>
+        <v>78279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7277,38 +7264,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555248</v>
+        <v>555370</v>
       </c>
       <c r="R60" t="n">
-        <v>6939350</v>
+        <v>6939656</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7354,7 +7341,15 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7376,10 +7371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215672</v>
+        <v>120215691</v>
       </c>
       <c r="B61" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7392,21 +7387,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7416,10 +7411,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555256</v>
+        <v>555287</v>
       </c>
       <c r="R61" t="n">
-        <v>6939301</v>
+        <v>6939378</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7465,7 +7460,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7487,10 +7482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215699</v>
+        <v>120215676</v>
       </c>
       <c r="B62" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7499,25 +7494,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7527,10 +7522,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555266</v>
+        <v>555303</v>
       </c>
       <c r="R62" t="n">
-        <v>6939388</v>
+        <v>6939259</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7576,7 +7571,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7598,7 +7593,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215676</v>
+        <v>120215669</v>
       </c>
       <c r="B63" t="n">
         <v>91858</v>
@@ -7638,10 +7633,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555303</v>
+        <v>555391</v>
       </c>
       <c r="R63" t="n">
-        <v>6939259</v>
+        <v>6939341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7709,10 +7704,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215687</v>
+        <v>120215743</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7721,38 +7716,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555260</v>
+        <v>555438</v>
       </c>
       <c r="R64" t="n">
-        <v>6939288</v>
+        <v>6939819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7798,15 +7793,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7828,10 +7815,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215742</v>
+        <v>120215681</v>
       </c>
       <c r="B65" t="n">
-        <v>90084</v>
+        <v>79160</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7840,38 +7827,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>256703</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555461</v>
+        <v>555310</v>
       </c>
       <c r="R65" t="n">
-        <v>6939822</v>
+        <v>6939320</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7917,7 +7904,12 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7939,10 +7931,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215663</v>
+        <v>120215740</v>
       </c>
       <c r="B66" t="n">
-        <v>91870</v>
+        <v>89292</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7951,38 +7943,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555335</v>
+        <v>555485</v>
       </c>
       <c r="R66" t="n">
-        <v>6939295</v>
+        <v>6939841</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8028,7 +8020,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8050,7 +8042,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215736</v>
+        <v>120215709</v>
       </c>
       <c r="B67" t="n">
         <v>91858</v>
@@ -8090,10 +8082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555530</v>
+        <v>555350</v>
       </c>
       <c r="R67" t="n">
-        <v>6939888</v>
+        <v>6939568</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8139,7 +8131,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8161,10 +8153,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215696</v>
+        <v>120215699</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8173,25 +8165,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8201,10 +8193,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555200</v>
+        <v>555266</v>
       </c>
       <c r="R68" t="n">
-        <v>6939344</v>
+        <v>6939388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8250,7 +8242,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8272,10 +8264,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215709</v>
+        <v>120215683</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8284,38 +8276,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555350</v>
+        <v>555323</v>
       </c>
       <c r="R69" t="n">
-        <v>6939568</v>
+        <v>6939333</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8361,7 +8353,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8506,10 +8498,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215665</v>
+        <v>120215720</v>
       </c>
       <c r="B71" t="n">
-        <v>90416</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8518,38 +8510,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6020</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555444</v>
+        <v>555385</v>
       </c>
       <c r="R71" t="n">
-        <v>6939356</v>
+        <v>6939665</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8595,15 +8587,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8625,10 +8609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215712</v>
+        <v>120215719</v>
       </c>
       <c r="B72" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8641,21 +8625,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8665,10 +8649,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555317</v>
+        <v>555393</v>
       </c>
       <c r="R72" t="n">
-        <v>6939671</v>
+        <v>6939610</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8714,7 +8698,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8736,10 +8720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215705</v>
+        <v>120215693</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8748,25 +8732,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8776,10 +8760,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555220</v>
+        <v>555255</v>
       </c>
       <c r="R73" t="n">
-        <v>6939479</v>
+        <v>6939329</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8825,7 +8809,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8847,10 +8831,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215732</v>
+        <v>120215675</v>
       </c>
       <c r="B74" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8859,38 +8843,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555453</v>
+        <v>555371</v>
       </c>
       <c r="R74" t="n">
-        <v>6939688</v>
+        <v>6939272</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8936,7 +8920,15 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8958,10 +8950,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215706</v>
+        <v>120215666</v>
       </c>
       <c r="B75" t="n">
-        <v>91481</v>
+        <v>91839</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8970,38 +8962,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4745</v>
+        <v>6055</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555195</v>
+        <v>555418</v>
       </c>
       <c r="R75" t="n">
-        <v>6939463</v>
+        <v>6939343</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9047,7 +9039,15 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215715</v>
+        <v>120215735</v>
       </c>
       <c r="B76" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555320</v>
+        <v>555516</v>
       </c>
       <c r="R76" t="n">
-        <v>6939665</v>
+        <v>6939844</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215684</v>
+        <v>120215724</v>
       </c>
       <c r="B77" t="n">
         <v>91858</v>
@@ -9216,14 +9216,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555328</v>
+        <v>555408</v>
       </c>
       <c r="R77" t="n">
-        <v>6939359</v>
+        <v>6939701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9291,7 +9291,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215724</v>
+        <v>120215733</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555408</v>
+        <v>555508</v>
       </c>
       <c r="R78" t="n">
-        <v>6939701</v>
+        <v>6939693</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215703</v>
+        <v>120215664</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9414,25 +9414,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555338</v>
+        <v>555450</v>
       </c>
       <c r="R79" t="n">
-        <v>6939447</v>
+        <v>6939355</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9513,10 +9513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215680</v>
+        <v>120215711</v>
       </c>
       <c r="B80" t="n">
-        <v>90545</v>
+        <v>91904</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9525,38 +9525,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>232140</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555303</v>
+        <v>555311</v>
       </c>
       <c r="R80" t="n">
-        <v>6939247</v>
+        <v>6939662</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215726</v>
+        <v>120215677</v>
       </c>
       <c r="B81" t="n">
-        <v>91881</v>
+        <v>90084</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9641,38 +9641,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555445</v>
+        <v>555282</v>
       </c>
       <c r="R81" t="n">
-        <v>6939653</v>
+        <v>6939236</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215725</v>
+        <v>120215672</v>
       </c>
       <c r="B82" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9756,34 +9756,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555442</v>
+        <v>555256</v>
       </c>
       <c r="R82" t="n">
-        <v>6939660</v>
+        <v>6939301</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215719</v>
+        <v>120215738</v>
       </c>
       <c r="B83" t="n">
         <v>91858</v>
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555393</v>
+        <v>555480</v>
       </c>
       <c r="R83" t="n">
-        <v>6939610</v>
+        <v>6939802</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215673</v>
+        <v>120215662</v>
       </c>
       <c r="B84" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9974,25 +9974,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555256</v>
+        <v>555210</v>
       </c>
       <c r="R84" t="n">
-        <v>6939303</v>
+        <v>6939191</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10073,10 +10073,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215704</v>
+        <v>120215713</v>
       </c>
       <c r="B85" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10085,38 +10085,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555333</v>
+        <v>555307</v>
       </c>
       <c r="R85" t="n">
-        <v>6939465</v>
+        <v>6939679</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10184,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215697</v>
+        <v>120215706</v>
       </c>
       <c r="B86" t="n">
-        <v>89292</v>
+        <v>91481</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10196,38 +10196,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555218</v>
+        <v>555195</v>
       </c>
       <c r="R86" t="n">
-        <v>6939369</v>
+        <v>6939463</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215713</v>
+        <v>120215715</v>
       </c>
       <c r="B87" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10307,25 +10307,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555307</v>
+        <v>555320</v>
       </c>
       <c r="R87" t="n">
-        <v>6939679</v>
+        <v>6939665</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215731</v>
+        <v>120215721</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555532</v>
+        <v>555389</v>
       </c>
       <c r="R15" t="n">
-        <v>6939560</v>
+        <v>6939706</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2294,7 +2302,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215705</v>
+        <v>120215731</v>
       </c>
       <c r="B16" t="n">
         <v>91858</v>
@@ -2330,14 +2338,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555220</v>
+        <v>555532</v>
       </c>
       <c r="R16" t="n">
-        <v>6939479</v>
+        <v>6939560</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2391,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,7 +2413,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215736</v>
+        <v>120215705</v>
       </c>
       <c r="B17" t="n">
         <v>91858</v>
@@ -2441,14 +2449,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555530</v>
+        <v>555220</v>
       </c>
       <c r="R17" t="n">
-        <v>6939888</v>
+        <v>6939479</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2502,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2516,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215721</v>
+        <v>120215736</v>
       </c>
       <c r="B18" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2536,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555389</v>
+        <v>555530</v>
       </c>
       <c r="R18" t="n">
-        <v>6939706</v>
+        <v>6939888</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,15 +2613,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215728</v>
+        <v>120215729</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,21 +2984,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555484</v>
+        <v>555492</v>
       </c>
       <c r="R22" t="n">
-        <v>6939523</v>
+        <v>6939553</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3060,9 +3060,12 @@
           <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>körspår</t>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3314,10 +3317,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215729</v>
+        <v>120215728</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3330,21 +3333,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3354,10 +3357,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555492</v>
+        <v>555484</v>
       </c>
       <c r="R25" t="n">
-        <v>6939553</v>
+        <v>6939523</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,12 +3409,9 @@
           <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215726</v>
+        <v>120215680</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3445,38 +3445,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555445</v>
+        <v>555303</v>
       </c>
       <c r="R26" t="n">
-        <v>6939653</v>
+        <v>6939247</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3522,12 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3544,10 +3549,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215680</v>
+        <v>120215726</v>
       </c>
       <c r="B27" t="n">
-        <v>90545</v>
+        <v>91881</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,38 +3561,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555303</v>
+        <v>555445</v>
       </c>
       <c r="R27" t="n">
-        <v>6939247</v>
+        <v>6939653</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,12 +3638,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215668</v>
+        <v>120215682</v>
       </c>
       <c r="B34" t="n">
-        <v>79527</v>
+        <v>91874</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4338,25 +4338,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555394</v>
+        <v>555325</v>
       </c>
       <c r="R34" t="n">
-        <v>6939336</v>
+        <v>6939312</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4415,15 +4415,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4445,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215682</v>
+        <v>120215668</v>
       </c>
       <c r="B35" t="n">
-        <v>91874</v>
+        <v>79527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4457,25 +4449,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4485,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555325</v>
+        <v>555394</v>
       </c>
       <c r="R35" t="n">
-        <v>6939312</v>
+        <v>6939336</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4534,7 +4526,15 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215667</v>
+        <v>120215704</v>
       </c>
       <c r="B41" t="n">
-        <v>91850</v>
+        <v>91328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555412</v>
+        <v>555333</v>
       </c>
       <c r="R41" t="n">
-        <v>6939333</v>
+        <v>6939465</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215702</v>
+        <v>120215667</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5242,25 +5242,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555204</v>
+        <v>555412</v>
       </c>
       <c r="R42" t="n">
-        <v>6939401</v>
+        <v>6939333</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215727</v>
+        <v>120215702</v>
       </c>
       <c r="B43" t="n">
         <v>91858</v>
@@ -5377,14 +5377,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555438</v>
+        <v>555204</v>
       </c>
       <c r="R43" t="n">
-        <v>6939535</v>
+        <v>6939401</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215703</v>
+        <v>120215727</v>
       </c>
       <c r="B44" t="n">
         <v>91858</v>
@@ -5488,14 +5488,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555338</v>
+        <v>555438</v>
       </c>
       <c r="R44" t="n">
-        <v>6939447</v>
+        <v>6939535</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215704</v>
+        <v>120215703</v>
       </c>
       <c r="B45" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5575,25 +5575,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555333</v>
+        <v>555338</v>
       </c>
       <c r="R45" t="n">
-        <v>6939465</v>
+        <v>6939447</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215691</v>
+        <v>120215740</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7383,38 +7383,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555287</v>
+        <v>555485</v>
       </c>
       <c r="R61" t="n">
-        <v>6939378</v>
+        <v>6939841</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215676</v>
+        <v>120215681</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7494,25 +7494,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7522,10 +7522,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555303</v>
+        <v>555310</v>
       </c>
       <c r="R62" t="n">
-        <v>6939259</v>
+        <v>6939320</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7571,7 +7571,12 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7704,7 +7709,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215743</v>
+        <v>120215691</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7740,14 +7745,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555438</v>
+        <v>555287</v>
       </c>
       <c r="R64" t="n">
-        <v>6939819</v>
+        <v>6939378</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7793,7 +7798,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7815,10 +7820,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215681</v>
+        <v>120215676</v>
       </c>
       <c r="B65" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7827,25 +7832,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7855,10 +7860,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555310</v>
+        <v>555303</v>
       </c>
       <c r="R65" t="n">
-        <v>6939320</v>
+        <v>6939259</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7904,12 +7909,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7931,10 +7931,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215740</v>
+        <v>120215743</v>
       </c>
       <c r="B66" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7943,25 +7943,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7971,10 +7971,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555485</v>
+        <v>555438</v>
       </c>
       <c r="R66" t="n">
-        <v>6939841</v>
+        <v>6939819</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215709</v>
+        <v>120215699</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8054,38 +8054,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555350</v>
+        <v>555266</v>
       </c>
       <c r="R67" t="n">
-        <v>6939568</v>
+        <v>6939388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215699</v>
+        <v>120215683</v>
       </c>
       <c r="B68" t="n">
         <v>91874</v>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555266</v>
+        <v>555323</v>
       </c>
       <c r="R68" t="n">
-        <v>6939388</v>
+        <v>6939333</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215683</v>
+        <v>120215723</v>
       </c>
       <c r="B69" t="n">
-        <v>91874</v>
+        <v>91839</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,38 +8276,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>6055</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555323</v>
+        <v>555369</v>
       </c>
       <c r="R69" t="n">
-        <v>6939333</v>
+        <v>6939717</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8353,7 +8357,15 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8375,10 +8387,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215723</v>
+        <v>120215709</v>
       </c>
       <c r="B70" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8387,42 +8399,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555369</v>
+        <v>555350</v>
       </c>
       <c r="R70" t="n">
-        <v>6939717</v>
+        <v>6939568</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8468,15 +8476,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215735</v>
+        <v>120215711</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555516</v>
+        <v>555311</v>
       </c>
       <c r="R76" t="n">
-        <v>6939844</v>
+        <v>6939662</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9158,7 +9158,12 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9180,10 +9185,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215724</v>
+        <v>120215677</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9196,34 +9201,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555408</v>
+        <v>555282</v>
       </c>
       <c r="R77" t="n">
-        <v>6939701</v>
+        <v>6939236</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9269,7 +9274,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9291,10 +9296,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215733</v>
+        <v>120215672</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9307,34 +9312,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555508</v>
+        <v>555256</v>
       </c>
       <c r="R78" t="n">
-        <v>6939693</v>
+        <v>6939301</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9380,7 +9385,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9402,10 +9407,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215664</v>
+        <v>120215735</v>
       </c>
       <c r="B79" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9414,38 +9419,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555450</v>
+        <v>555516</v>
       </c>
       <c r="R79" t="n">
-        <v>6939355</v>
+        <v>6939844</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9491,7 +9496,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9513,10 +9518,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215711</v>
+        <v>120215724</v>
       </c>
       <c r="B80" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9525,25 +9530,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9553,10 +9558,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555311</v>
+        <v>555408</v>
       </c>
       <c r="R80" t="n">
-        <v>6939662</v>
+        <v>6939701</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9602,12 +9607,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>under gammal tallågerest</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215677</v>
+        <v>120215733</v>
       </c>
       <c r="B81" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9645,34 +9645,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555282</v>
+        <v>555508</v>
       </c>
       <c r="R81" t="n">
-        <v>6939236</v>
+        <v>6939693</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215672</v>
+        <v>120215664</v>
       </c>
       <c r="B82" t="n">
-        <v>90084</v>
+        <v>91850</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9752,25 +9752,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9780,10 +9780,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555256</v>
+        <v>555450</v>
       </c>
       <c r="R82" t="n">
-        <v>6939301</v>
+        <v>6939355</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215721</v>
+        <v>120215687</v>
       </c>
       <c r="B15" t="n">
         <v>78279</v>
@@ -2219,14 +2219,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555389</v>
+        <v>555260</v>
       </c>
       <c r="R15" t="n">
-        <v>6939706</v>
+        <v>6939288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215731</v>
+        <v>120215686</v>
       </c>
       <c r="B16" t="n">
         <v>91858</v>
@@ -2338,14 +2338,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555532</v>
+        <v>555296</v>
       </c>
       <c r="R16" t="n">
-        <v>6939560</v>
+        <v>6939306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215705</v>
+        <v>120215695</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,21 +2429,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555220</v>
+        <v>555248</v>
       </c>
       <c r="R17" t="n">
-        <v>6939479</v>
+        <v>6939350</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215736</v>
+        <v>120215696</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2560,14 +2560,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555530</v>
+        <v>555200</v>
       </c>
       <c r="R18" t="n">
-        <v>6939888</v>
+        <v>6939344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215673</v>
+        <v>120215692</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,25 +2647,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555256</v>
+        <v>555260</v>
       </c>
       <c r="R19" t="n">
-        <v>6939303</v>
+        <v>6939329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215695</v>
+        <v>120215699</v>
       </c>
       <c r="B20" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,25 +2758,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555248</v>
+        <v>555266</v>
       </c>
       <c r="R20" t="n">
-        <v>6939350</v>
+        <v>6939388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215686</v>
+        <v>120215706</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,38 +2869,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555296</v>
+        <v>555195</v>
       </c>
       <c r="R21" t="n">
-        <v>6939306</v>
+        <v>6939463</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215729</v>
+        <v>120215714</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,21 +2984,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555492</v>
+        <v>555320</v>
       </c>
       <c r="R22" t="n">
-        <v>6939553</v>
+        <v>6939663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215674</v>
+        <v>120215720</v>
       </c>
       <c r="B23" t="n">
-        <v>91042</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,38 +3099,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5467</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555331</v>
+        <v>555385</v>
       </c>
       <c r="R23" t="n">
-        <v>6939284</v>
+        <v>6939665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,15 +3176,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
-        </is>
-      </c>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3206,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215741</v>
+        <v>120215671</v>
       </c>
       <c r="B24" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3222,34 +3214,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555486</v>
+        <v>555366</v>
       </c>
       <c r="R24" t="n">
-        <v>6939852</v>
+        <v>6939325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3295,7 +3287,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3317,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215728</v>
+        <v>120215716</v>
       </c>
       <c r="B25" t="n">
-        <v>91850</v>
+        <v>89247</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,25 +3321,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3357,10 +3349,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555484</v>
+        <v>555321</v>
       </c>
       <c r="R25" t="n">
-        <v>6939523</v>
+        <v>6939670</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,12 +3398,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>körspår</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3433,10 +3420,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215680</v>
+        <v>120215663</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>91870</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,21 +3436,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3473,10 +3460,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555303</v>
+        <v>555335</v>
       </c>
       <c r="R26" t="n">
-        <v>6939247</v>
+        <v>6939295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,12 +3509,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3549,10 +3531,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215726</v>
+        <v>120215673</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,34 +3547,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555445</v>
+        <v>555256</v>
       </c>
       <c r="R27" t="n">
-        <v>6939653</v>
+        <v>6939303</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3638,7 +3620,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3660,10 +3642,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215708</v>
+        <v>120215664</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3672,38 +3654,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555296</v>
+        <v>555450</v>
       </c>
       <c r="R28" t="n">
-        <v>6939533</v>
+        <v>6939355</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3749,7 +3731,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3771,7 +3753,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215707</v>
+        <v>120215705</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3807,14 +3789,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555227</v>
+        <v>555220</v>
       </c>
       <c r="R29" t="n">
-        <v>6939530</v>
+        <v>6939479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3860,7 +3842,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3882,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215679</v>
+        <v>120215742</v>
       </c>
       <c r="B30" t="n">
-        <v>91850</v>
+        <v>90084</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,38 +3876,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>256703</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555272</v>
+        <v>555461</v>
       </c>
       <c r="R30" t="n">
-        <v>6939241</v>
+        <v>6939822</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3971,7 +3953,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3993,10 +3975,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215678</v>
+        <v>120215683</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4005,25 +3987,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4033,10 +4015,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555271</v>
+        <v>555323</v>
       </c>
       <c r="R31" t="n">
-        <v>6939246</v>
+        <v>6939333</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4082,7 +4064,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4104,10 +4086,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215732</v>
+        <v>120215715</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4116,25 +4098,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4144,10 +4126,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555453</v>
+        <v>555320</v>
       </c>
       <c r="R32" t="n">
-        <v>6939688</v>
+        <v>6939665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4193,7 +4175,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4215,10 +4197,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215671</v>
+        <v>120215704</v>
       </c>
       <c r="B33" t="n">
-        <v>91874</v>
+        <v>91328</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4227,25 +4209,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>1958</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4255,10 +4237,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555366</v>
+        <v>555333</v>
       </c>
       <c r="R33" t="n">
-        <v>6939325</v>
+        <v>6939465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4304,7 +4286,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4326,10 +4308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215682</v>
+        <v>120215669</v>
       </c>
       <c r="B34" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4338,25 +4320,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4366,10 +4348,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555325</v>
+        <v>555391</v>
       </c>
       <c r="R34" t="n">
-        <v>6939312</v>
+        <v>6939341</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4415,7 +4397,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4437,10 +4419,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215668</v>
+        <v>120215703</v>
       </c>
       <c r="B35" t="n">
-        <v>79527</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4453,21 +4435,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4477,10 +4459,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555394</v>
+        <v>555338</v>
       </c>
       <c r="R35" t="n">
-        <v>6939336</v>
+        <v>6939447</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4526,15 +4508,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4556,10 +4530,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215712</v>
+        <v>120215725</v>
       </c>
       <c r="B36" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4572,21 +4546,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4596,10 +4570,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555317</v>
+        <v>555442</v>
       </c>
       <c r="R36" t="n">
-        <v>6939671</v>
+        <v>6939660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4645,7 +4619,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4667,10 +4641,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215742</v>
+        <v>120215713</v>
       </c>
       <c r="B37" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4683,21 +4657,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4707,10 +4681,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555461</v>
+        <v>555307</v>
       </c>
       <c r="R37" t="n">
-        <v>6939822</v>
+        <v>6939679</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4756,7 +4730,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4778,10 +4752,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215688</v>
+        <v>120215679</v>
       </c>
       <c r="B38" t="n">
-        <v>90848</v>
+        <v>91850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4790,25 +4764,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4818,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555246</v>
+        <v>555272</v>
       </c>
       <c r="R38" t="n">
-        <v>6939300</v>
+        <v>6939241</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,15 +4841,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4897,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215670</v>
+        <v>120215665</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>90416</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4913,21 +4879,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>6020</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4937,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555366</v>
+        <v>555444</v>
       </c>
       <c r="R39" t="n">
-        <v>6939325</v>
+        <v>6939356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4986,7 +4952,15 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5008,7 +4982,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215694</v>
+        <v>120215743</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5044,14 +5018,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555239</v>
+        <v>555438</v>
       </c>
       <c r="R40" t="n">
-        <v>6939322</v>
+        <v>6939819</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5097,7 +5071,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5119,10 +5093,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215704</v>
+        <v>120215691</v>
       </c>
       <c r="B41" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5131,25 +5105,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5159,10 +5133,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555333</v>
+        <v>555287</v>
       </c>
       <c r="R41" t="n">
-        <v>6939465</v>
+        <v>6939378</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5208,7 +5182,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5230,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215667</v>
+        <v>120215741</v>
       </c>
       <c r="B42" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5246,34 +5220,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555412</v>
+        <v>555486</v>
       </c>
       <c r="R42" t="n">
-        <v>6939333</v>
+        <v>6939852</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5319,7 +5293,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5341,7 +5315,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215702</v>
+        <v>120215735</v>
       </c>
       <c r="B43" t="n">
         <v>91858</v>
@@ -5377,14 +5351,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555204</v>
+        <v>555516</v>
       </c>
       <c r="R43" t="n">
-        <v>6939401</v>
+        <v>6939844</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5430,7 +5404,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5452,7 +5426,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215727</v>
+        <v>120215736</v>
       </c>
       <c r="B44" t="n">
         <v>91858</v>
@@ -5492,10 +5466,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555438</v>
+        <v>555530</v>
       </c>
       <c r="R44" t="n">
-        <v>6939535</v>
+        <v>6939888</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5541,7 +5515,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5563,10 +5537,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215703</v>
+        <v>120215666</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5575,25 +5549,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5603,10 +5577,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555338</v>
+        <v>555418</v>
       </c>
       <c r="R45" t="n">
-        <v>6939447</v>
+        <v>6939343</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5652,7 +5626,15 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5674,7 +5656,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215684</v>
+        <v>120215730</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5710,14 +5692,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555328</v>
+        <v>555499</v>
       </c>
       <c r="R46" t="n">
-        <v>6939359</v>
+        <v>6939547</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5763,7 +5745,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5785,10 +5767,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215663</v>
+        <v>120215719</v>
       </c>
       <c r="B47" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5801,34 +5783,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555335</v>
+        <v>555393</v>
       </c>
       <c r="R47" t="n">
-        <v>6939295</v>
+        <v>6939610</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5874,7 +5856,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5896,10 +5878,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120215730</v>
+        <v>120215674</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>91042</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5908,38 +5890,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555499</v>
+        <v>555331</v>
       </c>
       <c r="R48" t="n">
-        <v>6939547</v>
+        <v>6939284</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5985,7 +5967,15 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6007,7 +5997,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215722</v>
+        <v>120215694</v>
       </c>
       <c r="B49" t="n">
         <v>91858</v>
@@ -6043,14 +6033,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555358</v>
+        <v>555239</v>
       </c>
       <c r="R49" t="n">
-        <v>6939668</v>
+        <v>6939322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6096,7 +6086,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6118,7 +6108,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215696</v>
+        <v>120215733</v>
       </c>
       <c r="B50" t="n">
         <v>91858</v>
@@ -6154,14 +6144,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555200</v>
+        <v>555508</v>
       </c>
       <c r="R50" t="n">
-        <v>6939344</v>
+        <v>6939693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6207,7 +6197,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6229,10 +6219,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215690</v>
+        <v>120215721</v>
       </c>
       <c r="B51" t="n">
-        <v>91901</v>
+        <v>78279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6245,34 +6235,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555293</v>
+        <v>555389</v>
       </c>
       <c r="R51" t="n">
-        <v>6939349</v>
+        <v>6939706</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6318,7 +6308,15 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6340,10 +6338,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215665</v>
+        <v>120215702</v>
       </c>
       <c r="B52" t="n">
-        <v>90416</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6352,25 +6350,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6020</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6380,10 +6378,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555444</v>
+        <v>555204</v>
       </c>
       <c r="R52" t="n">
-        <v>6939356</v>
+        <v>6939401</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6429,15 +6427,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6459,10 +6449,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215716</v>
+        <v>120215676</v>
       </c>
       <c r="B53" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6471,38 +6461,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555321</v>
+        <v>555303</v>
       </c>
       <c r="R53" t="n">
-        <v>6939670</v>
+        <v>6939259</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6548,7 +6538,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6570,10 +6560,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215714</v>
+        <v>120215732</v>
       </c>
       <c r="B54" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6572,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,10 +6600,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555320</v>
+        <v>555453</v>
       </c>
       <c r="R54" t="n">
-        <v>6939663</v>
+        <v>6939688</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6659,15 +6649,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6689,10 +6671,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215697</v>
+        <v>120215726</v>
       </c>
       <c r="B55" t="n">
-        <v>89292</v>
+        <v>91881</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6701,38 +6683,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555218</v>
+        <v>555445</v>
       </c>
       <c r="R55" t="n">
-        <v>6939369</v>
+        <v>6939653</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6778,7 +6760,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6800,10 +6782,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215692</v>
+        <v>120215677</v>
       </c>
       <c r="B56" t="n">
-        <v>89292</v>
+        <v>90084</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6812,25 +6794,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6286</v>
+        <v>256703</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6840,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555260</v>
+        <v>555282</v>
       </c>
       <c r="R56" t="n">
-        <v>6939329</v>
+        <v>6939236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6889,7 +6871,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6911,10 +6893,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215725</v>
+        <v>120215680</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6927,34 +6909,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555442</v>
+        <v>555303</v>
       </c>
       <c r="R57" t="n">
-        <v>6939660</v>
+        <v>6939247</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7000,7 +6982,12 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7022,10 +7009,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215710</v>
+        <v>120215724</v>
       </c>
       <c r="B58" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7034,25 +7021,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7062,10 +7049,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555308</v>
+        <v>555408</v>
       </c>
       <c r="R58" t="n">
-        <v>6939650</v>
+        <v>6939701</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7111,7 +7098,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7133,10 +7120,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215687</v>
+        <v>120215708</v>
       </c>
       <c r="B59" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7145,38 +7132,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555260</v>
+        <v>555296</v>
       </c>
       <c r="R59" t="n">
-        <v>6939288</v>
+        <v>6939533</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7222,15 +7209,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7252,10 +7231,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215717</v>
+        <v>120215740</v>
       </c>
       <c r="B60" t="n">
-        <v>78279</v>
+        <v>89292</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7264,25 +7243,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7292,10 +7271,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555370</v>
+        <v>555485</v>
       </c>
       <c r="R60" t="n">
-        <v>6939656</v>
+        <v>6939841</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7341,15 +7320,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7371,10 +7342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215740</v>
+        <v>120215675</v>
       </c>
       <c r="B61" t="n">
-        <v>89292</v>
+        <v>92048</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7383,38 +7354,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555485</v>
+        <v>555371</v>
       </c>
       <c r="R61" t="n">
-        <v>6939841</v>
+        <v>6939272</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7460,7 +7431,15 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7598,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215669</v>
+        <v>120215682</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7610,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7638,10 +7617,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555391</v>
+        <v>555325</v>
       </c>
       <c r="R63" t="n">
-        <v>6939341</v>
+        <v>6939312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7687,7 +7666,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7709,7 +7688,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215691</v>
+        <v>120215709</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7745,14 +7724,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555287</v>
+        <v>555350</v>
       </c>
       <c r="R64" t="n">
-        <v>6939378</v>
+        <v>6939568</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7798,7 +7777,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7820,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215676</v>
+        <v>120215670</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7832,25 +7811,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7860,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555303</v>
+        <v>555366</v>
       </c>
       <c r="R65" t="n">
-        <v>6939259</v>
+        <v>6939325</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7931,10 +7910,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215743</v>
+        <v>120215717</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7943,25 +7922,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7971,10 +7950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555438</v>
+        <v>555370</v>
       </c>
       <c r="R66" t="n">
-        <v>6939819</v>
+        <v>6939656</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8020,7 +7999,15 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8042,10 +8029,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215699</v>
+        <v>120215731</v>
       </c>
       <c r="B67" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8054,38 +8041,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555266</v>
+        <v>555532</v>
       </c>
       <c r="R67" t="n">
-        <v>6939388</v>
+        <v>6939560</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8131,7 +8118,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8153,10 +8140,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215683</v>
+        <v>120215707</v>
       </c>
       <c r="B68" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8165,38 +8152,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555323</v>
+        <v>555227</v>
       </c>
       <c r="R68" t="n">
-        <v>6939333</v>
+        <v>6939530</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8242,7 +8229,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8264,10 +8251,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215723</v>
+        <v>120215711</v>
       </c>
       <c r="B69" t="n">
-        <v>91839</v>
+        <v>91904</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8280,38 +8267,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6055</v>
+        <v>232140</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555369</v>
+        <v>555311</v>
       </c>
       <c r="R69" t="n">
-        <v>6939717</v>
+        <v>6939662</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8357,15 +8340,12 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN69" t="n">
-        <v>1</v>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8387,10 +8367,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215709</v>
+        <v>120215712</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8403,21 +8383,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8427,10 +8407,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555350</v>
+        <v>555317</v>
       </c>
       <c r="R70" t="n">
-        <v>6939568</v>
+        <v>6939671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8476,7 +8456,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8498,10 +8478,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215720</v>
+        <v>120215710</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8510,25 +8490,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8538,10 +8518,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555385</v>
+        <v>555308</v>
       </c>
       <c r="R71" t="n">
-        <v>6939665</v>
+        <v>6939650</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8587,7 +8567,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8609,10 +8589,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215719</v>
+        <v>120215693</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8621,38 +8601,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555393</v>
+        <v>555255</v>
       </c>
       <c r="R72" t="n">
-        <v>6939610</v>
+        <v>6939329</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8698,7 +8678,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8720,10 +8700,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215693</v>
+        <v>120215684</v>
       </c>
       <c r="B73" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8732,25 +8712,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8760,10 +8740,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555255</v>
+        <v>555328</v>
       </c>
       <c r="R73" t="n">
-        <v>6939329</v>
+        <v>6939359</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8809,7 +8789,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8831,10 +8811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215675</v>
+        <v>120215678</v>
       </c>
       <c r="B74" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8843,25 +8823,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8871,10 +8851,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555371</v>
+        <v>555271</v>
       </c>
       <c r="R74" t="n">
-        <v>6939272</v>
+        <v>6939246</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8920,15 +8900,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8950,7 +8922,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215666</v>
+        <v>120215723</v>
       </c>
       <c r="B75" t="n">
         <v>91839</v>
@@ -8983,17 +8955,21 @@
           <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555418</v>
+        <v>555369</v>
       </c>
       <c r="R75" t="n">
-        <v>6939343</v>
+        <v>6939717</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9039,7 +9015,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AN75" t="n">
@@ -9047,7 +9023,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9069,10 +9045,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215711</v>
+        <v>120215688</v>
       </c>
       <c r="B76" t="n">
-        <v>91904</v>
+        <v>90848</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9081,38 +9057,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>232140</v>
+        <v>71</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555311</v>
+        <v>555246</v>
       </c>
       <c r="R76" t="n">
-        <v>6939662</v>
+        <v>6939300</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9158,12 +9134,15 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN76" t="n">
+        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>under gammal tallågerest</t>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9185,10 +9164,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215677</v>
+        <v>120215667</v>
       </c>
       <c r="B77" t="n">
-        <v>90084</v>
+        <v>91850</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9197,25 +9176,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9225,10 +9204,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555282</v>
+        <v>555412</v>
       </c>
       <c r="R77" t="n">
-        <v>6939236</v>
+        <v>6939333</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9274,7 +9253,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9296,10 +9275,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215672</v>
+        <v>120215728</v>
       </c>
       <c r="B78" t="n">
-        <v>90084</v>
+        <v>91850</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9308,38 +9287,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555256</v>
+        <v>555484</v>
       </c>
       <c r="R78" t="n">
-        <v>6939301</v>
+        <v>6939523</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9385,7 +9364,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9407,10 +9391,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215735</v>
+        <v>120215697</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9419,38 +9403,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555516</v>
+        <v>555218</v>
       </c>
       <c r="R79" t="n">
-        <v>6939844</v>
+        <v>6939369</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9496,7 +9480,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9518,7 +9502,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215724</v>
+        <v>120215722</v>
       </c>
       <c r="B80" t="n">
         <v>91858</v>
@@ -9558,10 +9542,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555408</v>
+        <v>555358</v>
       </c>
       <c r="R80" t="n">
-        <v>6939701</v>
+        <v>6939668</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9607,7 +9591,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9629,10 +9613,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215733</v>
+        <v>120215729</v>
       </c>
       <c r="B81" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9641,25 +9625,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9669,10 +9653,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555508</v>
+        <v>555492</v>
       </c>
       <c r="R81" t="n">
-        <v>6939693</v>
+        <v>6939553</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9718,7 +9702,15 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9740,10 +9732,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215664</v>
+        <v>120215727</v>
       </c>
       <c r="B82" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9752,38 +9744,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555450</v>
+        <v>555438</v>
       </c>
       <c r="R82" t="n">
-        <v>6939355</v>
+        <v>6939535</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9829,7 +9821,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9962,10 +9954,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215662</v>
+        <v>120215668</v>
       </c>
       <c r="B84" t="n">
-        <v>91870</v>
+        <v>79527</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9978,21 +9970,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4366</v>
+        <v>6456</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10002,10 +9994,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555210</v>
+        <v>555394</v>
       </c>
       <c r="R84" t="n">
-        <v>6939191</v>
+        <v>6939336</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10051,7 +10043,15 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10073,10 +10073,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215713</v>
+        <v>120215690</v>
       </c>
       <c r="B85" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10085,38 +10085,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555307</v>
+        <v>555293</v>
       </c>
       <c r="R85" t="n">
-        <v>6939679</v>
+        <v>6939349</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10184,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215706</v>
+        <v>120215662</v>
       </c>
       <c r="B86" t="n">
-        <v>91481</v>
+        <v>91870</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10196,38 +10196,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555195</v>
+        <v>555210</v>
       </c>
       <c r="R86" t="n">
-        <v>6939463</v>
+        <v>6939191</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215715</v>
+        <v>120215672</v>
       </c>
       <c r="B87" t="n">
-        <v>91328</v>
+        <v>90084</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10307,38 +10307,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1958</v>
+        <v>256703</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555320</v>
+        <v>555256</v>
       </c>
       <c r="R87" t="n">
-        <v>6939665</v>
+        <v>6939301</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -4197,10 +4197,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215704</v>
+        <v>120215665</v>
       </c>
       <c r="B33" t="n">
-        <v>91328</v>
+        <v>90416</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4209,25 +4209,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1958</v>
+        <v>6020</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555333</v>
+        <v>555444</v>
       </c>
       <c r="R33" t="n">
-        <v>6939465</v>
+        <v>6939356</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4286,15 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4308,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215669</v>
+        <v>120215704</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4320,25 +4328,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4348,10 +4356,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555391</v>
+        <v>555333</v>
       </c>
       <c r="R34" t="n">
-        <v>6939341</v>
+        <v>6939465</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4397,7 +4405,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4419,7 +4427,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215703</v>
+        <v>120215669</v>
       </c>
       <c r="B35" t="n">
         <v>91858</v>
@@ -4459,10 +4467,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555338</v>
+        <v>555391</v>
       </c>
       <c r="R35" t="n">
-        <v>6939447</v>
+        <v>6939341</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4508,7 +4516,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4530,7 +4538,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215725</v>
+        <v>120215703</v>
       </c>
       <c r="B36" t="n">
         <v>91858</v>
@@ -4566,14 +4574,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555442</v>
+        <v>555338</v>
       </c>
       <c r="R36" t="n">
-        <v>6939660</v>
+        <v>6939447</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4619,7 +4627,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4641,7 +4649,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215713</v>
+        <v>120215725</v>
       </c>
       <c r="B37" t="n">
         <v>91858</v>
@@ -4681,10 +4689,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555307</v>
+        <v>555442</v>
       </c>
       <c r="R37" t="n">
-        <v>6939679</v>
+        <v>6939660</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4730,7 +4738,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4752,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215679</v>
+        <v>120215713</v>
       </c>
       <c r="B38" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4764,38 +4772,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555272</v>
+        <v>555307</v>
       </c>
       <c r="R38" t="n">
-        <v>6939241</v>
+        <v>6939679</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4841,7 +4849,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4863,10 +4871,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215665</v>
+        <v>120215679</v>
       </c>
       <c r="B39" t="n">
-        <v>90416</v>
+        <v>91850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,21 +4887,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6020</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4903,10 +4911,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555444</v>
+        <v>555272</v>
       </c>
       <c r="R39" t="n">
-        <v>6939356</v>
+        <v>6939241</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4952,15 +4960,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215735</v>
+        <v>120215666</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,38 +5327,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555516</v>
+        <v>555418</v>
       </c>
       <c r="R43" t="n">
-        <v>6939844</v>
+        <v>6939343</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5404,7 +5404,15 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5426,7 +5434,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215736</v>
+        <v>120215735</v>
       </c>
       <c r="B44" t="n">
         <v>91858</v>
@@ -5466,10 +5474,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555530</v>
+        <v>555516</v>
       </c>
       <c r="R44" t="n">
-        <v>6939888</v>
+        <v>6939844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5515,7 +5523,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5537,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215666</v>
+        <v>120215736</v>
       </c>
       <c r="B45" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5549,38 +5557,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555418</v>
+        <v>555530</v>
       </c>
       <c r="R45" t="n">
-        <v>6939343</v>
+        <v>6939888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5626,15 +5634,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215724</v>
+        <v>120215675</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7021,38 +7021,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555408</v>
+        <v>555371</v>
       </c>
       <c r="R58" t="n">
-        <v>6939701</v>
+        <v>6939272</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7098,7 +7098,15 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7120,7 +7128,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215708</v>
+        <v>120215724</v>
       </c>
       <c r="B59" t="n">
         <v>91858</v>
@@ -7160,10 +7168,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555296</v>
+        <v>555408</v>
       </c>
       <c r="R59" t="n">
-        <v>6939533</v>
+        <v>6939701</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7209,7 +7217,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7231,10 +7239,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215740</v>
+        <v>120215708</v>
       </c>
       <c r="B60" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7243,25 +7251,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7271,10 +7279,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555485</v>
+        <v>555296</v>
       </c>
       <c r="R60" t="n">
-        <v>6939841</v>
+        <v>6939533</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7320,7 +7328,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7342,10 +7350,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215675</v>
+        <v>120215740</v>
       </c>
       <c r="B61" t="n">
-        <v>92048</v>
+        <v>89292</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7354,38 +7362,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555371</v>
+        <v>555485</v>
       </c>
       <c r="R61" t="n">
-        <v>6939272</v>
+        <v>6939841</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7431,15 +7439,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215693</v>
+        <v>120215723</v>
       </c>
       <c r="B72" t="n">
-        <v>91850</v>
+        <v>91839</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8601,38 +8601,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4361</v>
+        <v>6055</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555255</v>
+        <v>555369</v>
       </c>
       <c r="R72" t="n">
-        <v>6939329</v>
+        <v>6939717</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8678,7 +8682,15 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8700,10 +8712,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215684</v>
+        <v>120215693</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8712,25 +8724,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8740,10 +8752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555328</v>
+        <v>555255</v>
       </c>
       <c r="R73" t="n">
-        <v>6939359</v>
+        <v>6939329</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8789,7 +8801,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8811,7 +8823,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215678</v>
+        <v>120215684</v>
       </c>
       <c r="B74" t="n">
         <v>91858</v>
@@ -8851,10 +8863,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555271</v>
+        <v>555328</v>
       </c>
       <c r="R74" t="n">
-        <v>6939246</v>
+        <v>6939359</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8900,7 +8912,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8922,10 +8934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215723</v>
+        <v>120215678</v>
       </c>
       <c r="B75" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8934,42 +8946,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555369</v>
+        <v>555271</v>
       </c>
       <c r="R75" t="n">
-        <v>6939717</v>
+        <v>6939246</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9015,15 +9023,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215688</v>
+        <v>120215667</v>
       </c>
       <c r="B76" t="n">
-        <v>90848</v>
+        <v>91850</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9057,25 +9057,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>71</v>
+        <v>4361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555246</v>
+        <v>555412</v>
       </c>
       <c r="R76" t="n">
-        <v>6939300</v>
+        <v>6939333</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9134,15 +9134,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9164,7 +9156,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215667</v>
+        <v>120215728</v>
       </c>
       <c r="B77" t="n">
         <v>91850</v>
@@ -9200,14 +9192,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555412</v>
+        <v>555484</v>
       </c>
       <c r="R77" t="n">
-        <v>6939333</v>
+        <v>6939523</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9253,7 +9245,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9275,10 +9272,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215728</v>
+        <v>120215688</v>
       </c>
       <c r="B78" t="n">
-        <v>91850</v>
+        <v>90848</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9287,38 +9284,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4361</v>
+        <v>71</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555484</v>
+        <v>555246</v>
       </c>
       <c r="R78" t="n">
-        <v>6939523</v>
+        <v>6939300</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9364,12 +9361,15 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN78" t="n">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>körspår</t>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9732,10 +9732,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215727</v>
+        <v>120215690</v>
       </c>
       <c r="B82" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,38 +9744,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555438</v>
+        <v>555293</v>
       </c>
       <c r="R82" t="n">
-        <v>6939535</v>
+        <v>6939349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215738</v>
+        <v>120215668</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9859,34 +9859,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555480</v>
+        <v>555394</v>
       </c>
       <c r="R83" t="n">
-        <v>6939802</v>
+        <v>6939336</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9932,7 +9932,15 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9954,10 +9962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215668</v>
+        <v>120215662</v>
       </c>
       <c r="B84" t="n">
-        <v>79527</v>
+        <v>91870</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9970,21 +9978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9994,10 +10002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555394</v>
+        <v>555210</v>
       </c>
       <c r="R84" t="n">
-        <v>6939336</v>
+        <v>6939191</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,15 +10051,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10073,10 +10073,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215690</v>
+        <v>120215727</v>
       </c>
       <c r="B85" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10085,38 +10085,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555293</v>
+        <v>555438</v>
       </c>
       <c r="R85" t="n">
-        <v>6939349</v>
+        <v>6939535</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10184,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215662</v>
+        <v>120215738</v>
       </c>
       <c r="B86" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10200,34 +10200,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555210</v>
+        <v>555480</v>
       </c>
       <c r="R86" t="n">
-        <v>6939191</v>
+        <v>6939802</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215687</v>
+        <v>120215724</v>
       </c>
       <c r="B15" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,38 +2195,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555260</v>
+        <v>555408</v>
       </c>
       <c r="R15" t="n">
-        <v>6939288</v>
+        <v>6939701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,15 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2302,7 +2294,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215686</v>
+        <v>120215713</v>
       </c>
       <c r="B16" t="n">
         <v>91858</v>
@@ -2338,14 +2330,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555296</v>
+        <v>555307</v>
       </c>
       <c r="R16" t="n">
-        <v>6939306</v>
+        <v>6939679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,7 +2383,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2413,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215695</v>
+        <v>120215730</v>
       </c>
       <c r="B17" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,34 +2421,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555248</v>
+        <v>555499</v>
       </c>
       <c r="R17" t="n">
-        <v>6939350</v>
+        <v>6939547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2494,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2524,7 +2516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215696</v>
+        <v>120215725</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2560,14 +2552,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555200</v>
+        <v>555442</v>
       </c>
       <c r="R18" t="n">
-        <v>6939344</v>
+        <v>6939660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2605,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2635,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215692</v>
+        <v>120215736</v>
       </c>
       <c r="B19" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,38 +2639,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555260</v>
+        <v>555530</v>
       </c>
       <c r="R19" t="n">
-        <v>6939329</v>
+        <v>6939888</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2716,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2746,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215699</v>
+        <v>120215681</v>
       </c>
       <c r="B20" t="n">
-        <v>91874</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2762,21 +2754,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2786,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555266</v>
+        <v>555310</v>
       </c>
       <c r="R20" t="n">
-        <v>6939388</v>
+        <v>6939320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2827,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2857,10 +2854,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215706</v>
+        <v>120215711</v>
       </c>
       <c r="B21" t="n">
-        <v>91481</v>
+        <v>91904</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,38 +2866,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>232140</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555195</v>
+        <v>555311</v>
       </c>
       <c r="R21" t="n">
-        <v>6939463</v>
+        <v>6939662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2943,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2968,10 +2970,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215714</v>
+        <v>120215673</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,34 +2986,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555320</v>
+        <v>555256</v>
       </c>
       <c r="R22" t="n">
-        <v>6939663</v>
+        <v>6939303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,15 +3059,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3087,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215720</v>
+        <v>120215728</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,25 +3093,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3127,10 +3121,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555385</v>
+        <v>555484</v>
       </c>
       <c r="R23" t="n">
-        <v>6939665</v>
+        <v>6939523</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,7 +3170,12 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3198,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215671</v>
+        <v>120215664</v>
       </c>
       <c r="B24" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,21 +3213,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3237,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555366</v>
+        <v>555450</v>
       </c>
       <c r="R24" t="n">
-        <v>6939325</v>
+        <v>6939355</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3286,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3309,10 +3308,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215716</v>
+        <v>120215682</v>
       </c>
       <c r="B25" t="n">
-        <v>89247</v>
+        <v>91874</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,38 +3320,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1596</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555321</v>
+        <v>555325</v>
       </c>
       <c r="R25" t="n">
-        <v>6939670</v>
+        <v>6939312</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,7 +3397,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3420,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215663</v>
+        <v>120215690</v>
       </c>
       <c r="B26" t="n">
-        <v>91870</v>
+        <v>91901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,25 +3431,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3460,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555335</v>
+        <v>555293</v>
       </c>
       <c r="R26" t="n">
-        <v>6939295</v>
+        <v>6939349</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3508,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3531,10 +3530,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215673</v>
+        <v>120215691</v>
       </c>
       <c r="B27" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3543,25 +3542,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3571,10 +3570,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555256</v>
+        <v>555287</v>
       </c>
       <c r="R27" t="n">
-        <v>6939303</v>
+        <v>6939378</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3620,7 +3619,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3642,10 +3641,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215664</v>
+        <v>120215695</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,25 +3653,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3681,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555450</v>
+        <v>555248</v>
       </c>
       <c r="R28" t="n">
-        <v>6939355</v>
+        <v>6939350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3730,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3753,7 +3752,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215705</v>
+        <v>120215686</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3793,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555220</v>
+        <v>555296</v>
       </c>
       <c r="R29" t="n">
-        <v>6939479</v>
+        <v>6939306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3842,7 +3841,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3864,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215742</v>
+        <v>120215714</v>
       </c>
       <c r="B30" t="n">
-        <v>90084</v>
+        <v>78187</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,25 +3875,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>256703</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3903,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555461</v>
+        <v>555320</v>
       </c>
       <c r="R30" t="n">
-        <v>6939822</v>
+        <v>6939663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3953,7 +3952,15 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3975,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215683</v>
+        <v>120215740</v>
       </c>
       <c r="B31" t="n">
-        <v>91874</v>
+        <v>89292</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,38 +3994,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555323</v>
+        <v>555485</v>
       </c>
       <c r="R31" t="n">
-        <v>6939333</v>
+        <v>6939841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4064,7 +4071,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4086,10 +4093,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215715</v>
+        <v>120215729</v>
       </c>
       <c r="B32" t="n">
-        <v>91328</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4098,25 +4105,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1958</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4126,10 +4133,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555320</v>
+        <v>555492</v>
       </c>
       <c r="R32" t="n">
-        <v>6939665</v>
+        <v>6939553</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4175,7 +4182,15 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4197,10 +4212,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215665</v>
+        <v>120215697</v>
       </c>
       <c r="B33" t="n">
-        <v>90416</v>
+        <v>89292</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4209,25 +4224,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6020</v>
+        <v>6286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4237,10 +4252,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555444</v>
+        <v>555218</v>
       </c>
       <c r="R33" t="n">
-        <v>6939356</v>
+        <v>6939369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,15 +4301,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4316,10 +4323,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215704</v>
+        <v>120215665</v>
       </c>
       <c r="B34" t="n">
-        <v>91328</v>
+        <v>90416</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4328,25 +4335,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1958</v>
+        <v>6020</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4356,10 +4363,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555333</v>
+        <v>555444</v>
       </c>
       <c r="R34" t="n">
-        <v>6939465</v>
+        <v>6939356</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4405,7 +4412,15 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4427,10 +4442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215669</v>
+        <v>120215680</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4443,21 +4458,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4467,10 +4482,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555391</v>
+        <v>555303</v>
       </c>
       <c r="R35" t="n">
-        <v>6939341</v>
+        <v>6939247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4516,7 +4531,12 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4538,10 +4558,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215703</v>
+        <v>120215742</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4554,34 +4574,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555338</v>
+        <v>555461</v>
       </c>
       <c r="R36" t="n">
-        <v>6939447</v>
+        <v>6939822</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4627,7 +4647,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4649,7 +4669,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215725</v>
+        <v>120215719</v>
       </c>
       <c r="B37" t="n">
         <v>91858</v>
@@ -4689,10 +4709,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555442</v>
+        <v>555393</v>
       </c>
       <c r="R37" t="n">
-        <v>6939660</v>
+        <v>6939610</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4738,7 +4758,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4760,10 +4780,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215713</v>
+        <v>120215668</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4776,34 +4796,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555307</v>
+        <v>555394</v>
       </c>
       <c r="R38" t="n">
-        <v>6939679</v>
+        <v>6939336</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4849,7 +4869,15 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4871,10 +4899,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215679</v>
+        <v>120215699</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4887,21 +4915,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4911,10 +4939,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555272</v>
+        <v>555266</v>
       </c>
       <c r="R39" t="n">
-        <v>6939241</v>
+        <v>6939388</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4960,7 +4988,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4982,10 +5010,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215743</v>
+        <v>120215715</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4994,25 +5022,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5022,10 +5050,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555438</v>
+        <v>555320</v>
       </c>
       <c r="R40" t="n">
-        <v>6939819</v>
+        <v>6939665</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5071,7 +5099,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5093,10 +5121,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215691</v>
+        <v>120215663</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5109,21 +5137,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5133,10 +5161,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555287</v>
+        <v>555335</v>
       </c>
       <c r="R41" t="n">
-        <v>6939378</v>
+        <v>6939295</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5182,7 +5210,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5204,10 +5232,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215741</v>
+        <v>120215733</v>
       </c>
       <c r="B42" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5216,25 +5244,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5244,10 +5272,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555486</v>
+        <v>555508</v>
       </c>
       <c r="R42" t="n">
-        <v>6939852</v>
+        <v>6939693</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5321,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5315,10 +5343,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215666</v>
+        <v>120215706</v>
       </c>
       <c r="B43" t="n">
-        <v>91839</v>
+        <v>91481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,38 +5355,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6055</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555418</v>
+        <v>555195</v>
       </c>
       <c r="R43" t="n">
-        <v>6939343</v>
+        <v>6939463</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5404,15 +5432,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5434,10 +5454,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215735</v>
+        <v>120215712</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5450,21 +5470,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5474,10 +5494,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555516</v>
+        <v>555317</v>
       </c>
       <c r="R44" t="n">
-        <v>6939844</v>
+        <v>6939671</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5543,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5545,7 +5565,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215736</v>
+        <v>120215705</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5581,14 +5601,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555530</v>
+        <v>555220</v>
       </c>
       <c r="R45" t="n">
-        <v>6939888</v>
+        <v>6939479</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5634,7 +5654,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5656,7 +5676,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215730</v>
+        <v>120215707</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5696,10 +5716,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555499</v>
+        <v>555227</v>
       </c>
       <c r="R46" t="n">
-        <v>6939547</v>
+        <v>6939530</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5745,7 +5765,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5767,10 +5787,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215719</v>
+        <v>120215674</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>91042</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5779,38 +5799,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555393</v>
+        <v>555331</v>
       </c>
       <c r="R47" t="n">
-        <v>6939610</v>
+        <v>6939284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5856,7 +5876,15 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5878,10 +5906,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120215674</v>
+        <v>120215677</v>
       </c>
       <c r="B48" t="n">
-        <v>91042</v>
+        <v>90084</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5890,25 +5918,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5467</v>
+        <v>256703</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5918,10 +5946,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555331</v>
+        <v>555282</v>
       </c>
       <c r="R48" t="n">
-        <v>6939284</v>
+        <v>6939236</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5967,15 +5995,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5997,7 +6017,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215694</v>
+        <v>120215722</v>
       </c>
       <c r="B49" t="n">
         <v>91858</v>
@@ -6033,14 +6053,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555239</v>
+        <v>555358</v>
       </c>
       <c r="R49" t="n">
-        <v>6939322</v>
+        <v>6939668</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6086,7 +6106,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6108,10 +6128,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215733</v>
+        <v>120215721</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,25 +6140,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6148,10 +6168,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555508</v>
+        <v>555389</v>
       </c>
       <c r="R50" t="n">
-        <v>6939693</v>
+        <v>6939706</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6198,6 +6218,14 @@
       <c r="AI50" t="inlineStr">
         <is>
           <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6219,10 +6247,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215721</v>
+        <v>120215704</v>
       </c>
       <c r="B51" t="n">
-        <v>78279</v>
+        <v>91328</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6231,38 +6259,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>1958</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555389</v>
+        <v>555333</v>
       </c>
       <c r="R51" t="n">
-        <v>6939706</v>
+        <v>6939465</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6308,15 +6336,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6338,10 +6358,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215702</v>
+        <v>120215726</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6350,38 +6370,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555204</v>
+        <v>555445</v>
       </c>
       <c r="R52" t="n">
-        <v>6939401</v>
+        <v>6939653</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6427,7 +6447,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6449,10 +6469,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215676</v>
+        <v>120215692</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6461,25 +6481,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6489,10 +6509,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555303</v>
+        <v>555260</v>
       </c>
       <c r="R53" t="n">
-        <v>6939259</v>
+        <v>6939329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6538,7 +6558,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6560,10 +6580,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215732</v>
+        <v>120215662</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6576,34 +6596,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555453</v>
+        <v>555210</v>
       </c>
       <c r="R54" t="n">
-        <v>6939688</v>
+        <v>6939191</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6649,7 +6669,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6671,10 +6691,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215726</v>
+        <v>120215667</v>
       </c>
       <c r="B55" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6687,34 +6707,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555445</v>
+        <v>555412</v>
       </c>
       <c r="R55" t="n">
-        <v>6939653</v>
+        <v>6939333</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6760,7 +6780,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6782,10 +6802,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215677</v>
+        <v>120215675</v>
       </c>
       <c r="B56" t="n">
-        <v>90084</v>
+        <v>92048</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6794,25 +6814,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>256703</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6842,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555282</v>
+        <v>555371</v>
       </c>
       <c r="R56" t="n">
-        <v>6939236</v>
+        <v>6939272</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6872,6 +6892,14 @@
       <c r="AI56" t="inlineStr">
         <is>
           <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6893,10 +6921,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215680</v>
+        <v>120215687</v>
       </c>
       <c r="B57" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6905,25 +6933,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6933,10 +6961,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555303</v>
+        <v>555260</v>
       </c>
       <c r="R57" t="n">
-        <v>6939247</v>
+        <v>6939288</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6982,12 +7010,15 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN57" t="n">
+        <v>1</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7009,10 +7040,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215675</v>
+        <v>120215727</v>
       </c>
       <c r="B58" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7021,38 +7052,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555371</v>
+        <v>555438</v>
       </c>
       <c r="R58" t="n">
-        <v>6939272</v>
+        <v>6939535</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7098,15 +7129,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7128,10 +7151,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215724</v>
+        <v>120215683</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7140,38 +7163,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555408</v>
+        <v>555323</v>
       </c>
       <c r="R59" t="n">
-        <v>6939701</v>
+        <v>6939333</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7217,7 +7240,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7239,10 +7262,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215708</v>
+        <v>120215671</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7251,38 +7274,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555296</v>
+        <v>555366</v>
       </c>
       <c r="R60" t="n">
-        <v>6939533</v>
+        <v>6939325</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7328,7 +7351,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7350,10 +7373,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215740</v>
+        <v>120215688</v>
       </c>
       <c r="B61" t="n">
-        <v>89292</v>
+        <v>90848</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7362,38 +7385,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>71</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555485</v>
+        <v>555246</v>
       </c>
       <c r="R61" t="n">
-        <v>6939841</v>
+        <v>6939300</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7439,7 +7462,15 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7461,10 +7492,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215681</v>
+        <v>120215741</v>
       </c>
       <c r="B62" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7477,34 +7508,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555310</v>
+        <v>555486</v>
       </c>
       <c r="R62" t="n">
-        <v>6939320</v>
+        <v>6939852</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7550,12 +7581,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7577,10 +7603,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215682</v>
+        <v>120215731</v>
       </c>
       <c r="B63" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,38 +7615,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555325</v>
+        <v>555532</v>
       </c>
       <c r="R63" t="n">
-        <v>6939312</v>
+        <v>6939560</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7666,7 +7692,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7688,10 +7714,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215709</v>
+        <v>120215666</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7700,38 +7726,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555350</v>
+        <v>555418</v>
       </c>
       <c r="R64" t="n">
-        <v>6939568</v>
+        <v>6939343</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7777,7 +7803,15 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7799,10 +7833,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215670</v>
+        <v>120215694</v>
       </c>
       <c r="B65" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7811,25 +7845,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7873,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555366</v>
+        <v>555239</v>
       </c>
       <c r="R65" t="n">
-        <v>6939325</v>
+        <v>6939322</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7888,7 +7922,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7910,10 +7944,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215717</v>
+        <v>120215710</v>
       </c>
       <c r="B66" t="n">
-        <v>78279</v>
+        <v>89247</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7922,25 +7956,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>1596</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7950,10 +7984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555370</v>
+        <v>555308</v>
       </c>
       <c r="R66" t="n">
-        <v>6939656</v>
+        <v>6939650</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7999,15 +8033,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8029,10 +8055,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215731</v>
+        <v>120215672</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8045,34 +8071,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555532</v>
+        <v>555256</v>
       </c>
       <c r="R67" t="n">
-        <v>6939560</v>
+        <v>6939301</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8118,7 +8144,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8140,10 +8166,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215707</v>
+        <v>120215670</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8152,38 +8178,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555227</v>
+        <v>555366</v>
       </c>
       <c r="R68" t="n">
-        <v>6939530</v>
+        <v>6939325</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8229,7 +8255,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8251,10 +8277,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215711</v>
+        <v>120215708</v>
       </c>
       <c r="B69" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8263,25 +8289,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8291,10 +8317,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555311</v>
+        <v>555296</v>
       </c>
       <c r="R69" t="n">
-        <v>6939662</v>
+        <v>6939533</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8340,12 +8366,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>under gammal tallågerest</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8367,10 +8388,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215712</v>
+        <v>120215735</v>
       </c>
       <c r="B70" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8383,21 +8404,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8407,10 +8428,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555317</v>
+        <v>555516</v>
       </c>
       <c r="R70" t="n">
-        <v>6939671</v>
+        <v>6939844</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8456,7 +8477,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8478,10 +8499,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215710</v>
+        <v>120215738</v>
       </c>
       <c r="B71" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8490,25 +8511,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8518,10 +8539,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555308</v>
+        <v>555480</v>
       </c>
       <c r="R71" t="n">
-        <v>6939650</v>
+        <v>6939802</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8567,7 +8588,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8589,10 +8610,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215723</v>
+        <v>120215696</v>
       </c>
       <c r="B72" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8601,42 +8622,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555369</v>
+        <v>555200</v>
       </c>
       <c r="R72" t="n">
-        <v>6939717</v>
+        <v>6939344</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8682,15 +8699,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8712,10 +8721,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215693</v>
+        <v>120215702</v>
       </c>
       <c r="B73" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8724,25 +8733,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8752,10 +8761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555255</v>
+        <v>555204</v>
       </c>
       <c r="R73" t="n">
-        <v>6939329</v>
+        <v>6939401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8801,7 +8810,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8823,7 +8832,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215684</v>
+        <v>120215678</v>
       </c>
       <c r="B74" t="n">
         <v>91858</v>
@@ -8863,10 +8872,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555328</v>
+        <v>555271</v>
       </c>
       <c r="R74" t="n">
-        <v>6939359</v>
+        <v>6939246</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8912,7 +8921,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8934,7 +8943,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215678</v>
+        <v>120215709</v>
       </c>
       <c r="B75" t="n">
         <v>91858</v>
@@ -8970,14 +8979,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555271</v>
+        <v>555350</v>
       </c>
       <c r="R75" t="n">
-        <v>6939246</v>
+        <v>6939568</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9023,7 +9032,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9045,7 +9054,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215667</v>
+        <v>120215693</v>
       </c>
       <c r="B76" t="n">
         <v>91850</v>
@@ -9085,10 +9094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555412</v>
+        <v>555255</v>
       </c>
       <c r="R76" t="n">
-        <v>6939333</v>
+        <v>6939329</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9134,7 +9143,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9156,10 +9165,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215728</v>
+        <v>120215669</v>
       </c>
       <c r="B77" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9168,38 +9177,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555484</v>
+        <v>555391</v>
       </c>
       <c r="R77" t="n">
-        <v>6939523</v>
+        <v>6939341</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9245,12 +9254,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>körspår</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9272,10 +9276,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215688</v>
+        <v>120215732</v>
       </c>
       <c r="B78" t="n">
-        <v>90848</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9284,38 +9288,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555246</v>
+        <v>555453</v>
       </c>
       <c r="R78" t="n">
-        <v>6939300</v>
+        <v>6939688</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9361,15 +9365,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9391,10 +9387,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215697</v>
+        <v>120215743</v>
       </c>
       <c r="B79" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9403,38 +9399,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555218</v>
+        <v>555438</v>
       </c>
       <c r="R79" t="n">
-        <v>6939369</v>
+        <v>6939819</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9480,7 +9476,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9502,10 +9498,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215722</v>
+        <v>120215723</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9514,38 +9510,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555358</v>
+        <v>555369</v>
       </c>
       <c r="R80" t="n">
-        <v>6939668</v>
+        <v>6939717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9591,7 +9591,15 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9613,10 +9621,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215729</v>
+        <v>120215717</v>
       </c>
       <c r="B81" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9629,21 +9637,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9653,10 +9661,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555492</v>
+        <v>555370</v>
       </c>
       <c r="R81" t="n">
-        <v>6939553</v>
+        <v>6939656</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9702,7 +9710,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AN81" t="n">
@@ -9710,7 +9718,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9732,10 +9740,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215690</v>
+        <v>120215684</v>
       </c>
       <c r="B82" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,25 +9752,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9772,10 +9780,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555293</v>
+        <v>555328</v>
       </c>
       <c r="R82" t="n">
-        <v>6939349</v>
+        <v>6939359</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9821,7 +9829,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9843,10 +9851,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215668</v>
+        <v>120215679</v>
       </c>
       <c r="B83" t="n">
-        <v>79527</v>
+        <v>91850</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9855,25 +9863,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9883,10 +9891,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555394</v>
+        <v>555272</v>
       </c>
       <c r="R83" t="n">
-        <v>6939336</v>
+        <v>6939241</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9932,15 +9940,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215662</v>
+        <v>120215676</v>
       </c>
       <c r="B84" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9978,21 +9978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555210</v>
+        <v>555303</v>
       </c>
       <c r="R84" t="n">
-        <v>6939191</v>
+        <v>6939259</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10073,7 +10073,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215727</v>
+        <v>120215720</v>
       </c>
       <c r="B85" t="n">
         <v>91858</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555438</v>
+        <v>555385</v>
       </c>
       <c r="R85" t="n">
-        <v>6939535</v>
+        <v>6939665</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10184,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215738</v>
+        <v>120215716</v>
       </c>
       <c r="B86" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10196,25 +10196,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555480</v>
+        <v>555321</v>
       </c>
       <c r="R86" t="n">
-        <v>6939802</v>
+        <v>6939670</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215672</v>
+        <v>120215703</v>
       </c>
       <c r="B87" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10311,21 +10311,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555256</v>
+        <v>555338</v>
       </c>
       <c r="R87" t="n">
-        <v>6939301</v>
+        <v>6939447</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215724</v>
+        <v>120215694</v>
       </c>
       <c r="B15" t="n">
         <v>91858</v>
@@ -2219,14 +2219,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555408</v>
+        <v>555239</v>
       </c>
       <c r="R15" t="n">
-        <v>6939701</v>
+        <v>6939322</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215713</v>
+        <v>120215729</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555307</v>
+        <v>555492</v>
       </c>
       <c r="R16" t="n">
-        <v>6939679</v>
+        <v>6939553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2383,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215730</v>
+        <v>120215673</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,38 +2425,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555499</v>
+        <v>555256</v>
       </c>
       <c r="R17" t="n">
-        <v>6939547</v>
+        <v>6939303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2502,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2516,7 +2524,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215725</v>
+        <v>120215705</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2552,14 +2560,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555442</v>
+        <v>555220</v>
       </c>
       <c r="R18" t="n">
-        <v>6939660</v>
+        <v>6939479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2613,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2627,7 +2635,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215736</v>
+        <v>120215696</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2663,14 +2671,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555530</v>
+        <v>555200</v>
       </c>
       <c r="R19" t="n">
-        <v>6939888</v>
+        <v>6939344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2724,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2738,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215681</v>
+        <v>120215720</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,38 +2758,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555310</v>
+        <v>555385</v>
       </c>
       <c r="R20" t="n">
-        <v>6939320</v>
+        <v>6939665</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,12 +2835,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2854,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215711</v>
+        <v>120215664</v>
       </c>
       <c r="B21" t="n">
-        <v>91904</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,38 +2869,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>232140</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555311</v>
+        <v>555450</v>
       </c>
       <c r="R21" t="n">
-        <v>6939662</v>
+        <v>6939355</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,12 +2946,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>under gammal tallågerest</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2970,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215673</v>
+        <v>120215714</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,34 +2984,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555256</v>
+        <v>555320</v>
       </c>
       <c r="R22" t="n">
-        <v>6939303</v>
+        <v>6939663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3057,15 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3081,10 +3087,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215728</v>
+        <v>120215732</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3093,25 +3099,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3121,10 +3127,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555484</v>
+        <v>555453</v>
       </c>
       <c r="R23" t="n">
-        <v>6939523</v>
+        <v>6939688</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,12 +3176,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>körspår</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3197,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215664</v>
+        <v>120215681</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3213,21 +3214,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3237,10 +3238,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555450</v>
+        <v>555310</v>
       </c>
       <c r="R24" t="n">
-        <v>6939355</v>
+        <v>6939320</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3287,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3308,7 +3314,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215682</v>
+        <v>120215671</v>
       </c>
       <c r="B25" t="n">
         <v>91874</v>
@@ -3348,10 +3354,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555325</v>
+        <v>555366</v>
       </c>
       <c r="R25" t="n">
-        <v>6939312</v>
+        <v>6939325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,7 +3403,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3419,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215690</v>
+        <v>120215706</v>
       </c>
       <c r="B26" t="n">
-        <v>91901</v>
+        <v>91481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3435,34 +3441,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>4745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555293</v>
+        <v>555195</v>
       </c>
       <c r="R26" t="n">
-        <v>6939349</v>
+        <v>6939463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,7 +3514,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3530,7 +3536,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215691</v>
+        <v>120215736</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3566,14 +3572,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555287</v>
+        <v>555530</v>
       </c>
       <c r="R27" t="n">
-        <v>6939378</v>
+        <v>6939888</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,7 +3625,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3641,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215695</v>
+        <v>120215728</v>
       </c>
       <c r="B28" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3653,38 +3659,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555248</v>
+        <v>555484</v>
       </c>
       <c r="R28" t="n">
-        <v>6939350</v>
+        <v>6939523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3730,7 +3736,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3752,7 +3763,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215686</v>
+        <v>120215678</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3792,10 +3803,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555296</v>
+        <v>555271</v>
       </c>
       <c r="R29" t="n">
-        <v>6939306</v>
+        <v>6939246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,7 +3852,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3863,10 +3874,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215714</v>
+        <v>120215709</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,25 +3886,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3903,10 +3914,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555320</v>
+        <v>555350</v>
       </c>
       <c r="R30" t="n">
-        <v>6939663</v>
+        <v>6939568</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3952,15 +3963,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3982,10 +3985,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215740</v>
+        <v>120215687</v>
       </c>
       <c r="B31" t="n">
-        <v>89292</v>
+        <v>78279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3994,38 +3997,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555485</v>
+        <v>555260</v>
       </c>
       <c r="R31" t="n">
-        <v>6939841</v>
+        <v>6939288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4071,7 +4074,15 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4093,10 +4104,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215729</v>
+        <v>120215731</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4105,25 +4116,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4133,10 +4144,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555492</v>
+        <v>555532</v>
       </c>
       <c r="R32" t="n">
-        <v>6939553</v>
+        <v>6939560</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4182,15 +4193,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4212,10 +4215,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215697</v>
+        <v>120215743</v>
       </c>
       <c r="B33" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4224,38 +4227,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555218</v>
+        <v>555438</v>
       </c>
       <c r="R33" t="n">
-        <v>6939369</v>
+        <v>6939819</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4301,7 +4304,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4323,10 +4326,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215665</v>
+        <v>120215670</v>
       </c>
       <c r="B34" t="n">
-        <v>90416</v>
+        <v>91850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4339,21 +4342,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6020</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4363,10 +4366,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555444</v>
+        <v>555366</v>
       </c>
       <c r="R34" t="n">
-        <v>6939356</v>
+        <v>6939325</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4412,15 +4415,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4442,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215680</v>
+        <v>120215704</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>91328</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4454,25 +4449,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1958</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4482,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555303</v>
+        <v>555333</v>
       </c>
       <c r="R35" t="n">
-        <v>6939247</v>
+        <v>6939465</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4531,12 +4526,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4558,10 +4548,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215742</v>
+        <v>120215688</v>
       </c>
       <c r="B36" t="n">
-        <v>90084</v>
+        <v>90848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4570,38 +4560,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256703</v>
+        <v>71</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555461</v>
+        <v>555246</v>
       </c>
       <c r="R36" t="n">
-        <v>6939822</v>
+        <v>6939300</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4647,7 +4637,15 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4669,7 +4667,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215719</v>
+        <v>120215676</v>
       </c>
       <c r="B37" t="n">
         <v>91858</v>
@@ -4705,14 +4703,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555393</v>
+        <v>555303</v>
       </c>
       <c r="R37" t="n">
-        <v>6939610</v>
+        <v>6939259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4758,7 +4756,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4780,10 +4778,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215668</v>
+        <v>120215726</v>
       </c>
       <c r="B38" t="n">
-        <v>79527</v>
+        <v>91881</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4792,38 +4790,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555394</v>
+        <v>555445</v>
       </c>
       <c r="R38" t="n">
-        <v>6939336</v>
+        <v>6939653</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,15 +4867,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4899,10 +4889,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215699</v>
+        <v>120215719</v>
       </c>
       <c r="B39" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4911,38 +4901,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555266</v>
+        <v>555393</v>
       </c>
       <c r="R39" t="n">
-        <v>6939388</v>
+        <v>6939610</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4988,7 +4978,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5010,10 +5000,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215715</v>
+        <v>120215703</v>
       </c>
       <c r="B40" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5022,38 +5012,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555320</v>
+        <v>555338</v>
       </c>
       <c r="R40" t="n">
-        <v>6939665</v>
+        <v>6939447</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5099,7 +5089,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5121,10 +5111,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215663</v>
+        <v>120215682</v>
       </c>
       <c r="B41" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5133,25 +5123,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5161,10 +5151,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555335</v>
+        <v>555325</v>
       </c>
       <c r="R41" t="n">
-        <v>6939295</v>
+        <v>6939312</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5210,7 +5200,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5232,10 +5222,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215733</v>
+        <v>120215675</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5244,38 +5234,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555508</v>
+        <v>555371</v>
       </c>
       <c r="R42" t="n">
-        <v>6939693</v>
+        <v>6939272</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5321,7 +5311,15 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5343,10 +5341,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215706</v>
+        <v>120215674</v>
       </c>
       <c r="B43" t="n">
-        <v>91481</v>
+        <v>91042</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5359,34 +5357,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>5467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555195</v>
+        <v>555331</v>
       </c>
       <c r="R43" t="n">
-        <v>6939463</v>
+        <v>6939284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5432,7 +5430,15 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5454,10 +5460,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215712</v>
+        <v>120215690</v>
       </c>
       <c r="B44" t="n">
-        <v>90084</v>
+        <v>91901</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5466,38 +5472,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256703</v>
+        <v>5448</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555317</v>
+        <v>555293</v>
       </c>
       <c r="R44" t="n">
-        <v>6939671</v>
+        <v>6939349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5543,7 +5549,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5565,10 +5571,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215705</v>
+        <v>120215699</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5577,25 +5583,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5605,10 +5611,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555220</v>
+        <v>555266</v>
       </c>
       <c r="R45" t="n">
-        <v>6939479</v>
+        <v>6939388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5676,7 +5682,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215707</v>
+        <v>120215727</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5716,10 +5722,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555227</v>
+        <v>555438</v>
       </c>
       <c r="R46" t="n">
-        <v>6939530</v>
+        <v>6939535</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5765,7 +5771,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5787,10 +5793,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215674</v>
+        <v>120215708</v>
       </c>
       <c r="B47" t="n">
-        <v>91042</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5799,38 +5805,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5467</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555331</v>
+        <v>555296</v>
       </c>
       <c r="R47" t="n">
-        <v>6939284</v>
+        <v>6939533</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5876,15 +5882,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5906,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120215677</v>
+        <v>120215692</v>
       </c>
       <c r="B48" t="n">
-        <v>90084</v>
+        <v>89292</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5918,25 +5916,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>256703</v>
+        <v>6286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5946,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555282</v>
+        <v>555260</v>
       </c>
       <c r="R48" t="n">
-        <v>6939236</v>
+        <v>6939329</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5995,7 +5993,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6017,7 +6015,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215722</v>
+        <v>120215669</v>
       </c>
       <c r="B49" t="n">
         <v>91858</v>
@@ -6053,14 +6051,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555358</v>
+        <v>555391</v>
       </c>
       <c r="R49" t="n">
-        <v>6939668</v>
+        <v>6939341</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6106,7 +6104,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6128,10 +6126,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215721</v>
+        <v>120215724</v>
       </c>
       <c r="B50" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6140,25 +6138,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6168,10 +6166,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555389</v>
+        <v>555408</v>
       </c>
       <c r="R50" t="n">
-        <v>6939706</v>
+        <v>6939701</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6217,15 +6215,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6247,10 +6237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215704</v>
+        <v>120215691</v>
       </c>
       <c r="B51" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6259,25 +6249,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6287,10 +6277,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555333</v>
+        <v>555287</v>
       </c>
       <c r="R51" t="n">
-        <v>6939465</v>
+        <v>6939378</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6336,7 +6326,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6358,10 +6348,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215726</v>
+        <v>120215740</v>
       </c>
       <c r="B52" t="n">
-        <v>91881</v>
+        <v>89292</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6370,25 +6360,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6398,10 +6388,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555445</v>
+        <v>555485</v>
       </c>
       <c r="R52" t="n">
-        <v>6939653</v>
+        <v>6939841</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6447,7 +6437,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6469,10 +6459,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215692</v>
+        <v>120215738</v>
       </c>
       <c r="B53" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6481,38 +6471,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555260</v>
+        <v>555480</v>
       </c>
       <c r="R53" t="n">
-        <v>6939329</v>
+        <v>6939802</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6558,7 +6548,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6580,10 +6570,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215662</v>
+        <v>120215713</v>
       </c>
       <c r="B54" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6596,34 +6586,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555210</v>
+        <v>555307</v>
       </c>
       <c r="R54" t="n">
-        <v>6939191</v>
+        <v>6939679</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6669,7 +6659,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6691,10 +6681,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215667</v>
+        <v>120215722</v>
       </c>
       <c r="B55" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6703,38 +6693,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555412</v>
+        <v>555358</v>
       </c>
       <c r="R55" t="n">
-        <v>6939333</v>
+        <v>6939668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6780,7 +6770,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6802,10 +6792,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215675</v>
+        <v>120215721</v>
       </c>
       <c r="B56" t="n">
-        <v>92048</v>
+        <v>78279</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6818,34 +6808,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555371</v>
+        <v>555389</v>
       </c>
       <c r="R56" t="n">
-        <v>6939272</v>
+        <v>6939706</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6891,7 +6881,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AN56" t="n">
@@ -6899,7 +6889,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6921,7 +6911,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215687</v>
+        <v>120215717</v>
       </c>
       <c r="B57" t="n">
         <v>78279</v>
@@ -6957,14 +6947,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555260</v>
+        <v>555370</v>
       </c>
       <c r="R57" t="n">
-        <v>6939288</v>
+        <v>6939656</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7010,7 +7000,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AN57" t="n">
@@ -7018,7 +7008,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7040,10 +7030,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215727</v>
+        <v>120215712</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7056,21 +7046,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7080,10 +7070,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555438</v>
+        <v>555317</v>
       </c>
       <c r="R58" t="n">
-        <v>6939535</v>
+        <v>6939671</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7129,7 +7119,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7151,10 +7141,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215683</v>
+        <v>120215672</v>
       </c>
       <c r="B59" t="n">
-        <v>91874</v>
+        <v>90084</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7163,25 +7153,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7191,10 +7181,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555323</v>
+        <v>555256</v>
       </c>
       <c r="R59" t="n">
-        <v>6939333</v>
+        <v>6939301</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7240,7 +7230,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7262,10 +7252,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215671</v>
+        <v>120215677</v>
       </c>
       <c r="B60" t="n">
-        <v>91874</v>
+        <v>90084</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7274,25 +7264,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7302,10 +7292,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555366</v>
+        <v>555282</v>
       </c>
       <c r="R60" t="n">
-        <v>6939325</v>
+        <v>6939236</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7373,10 +7363,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215688</v>
+        <v>120215711</v>
       </c>
       <c r="B61" t="n">
-        <v>90848</v>
+        <v>91904</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7385,38 +7375,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>71</v>
+        <v>232140</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555246</v>
+        <v>555311</v>
       </c>
       <c r="R61" t="n">
-        <v>6939300</v>
+        <v>6939662</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7462,15 +7452,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN61" t="n">
-        <v>1</v>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7492,10 +7479,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215741</v>
+        <v>120215679</v>
       </c>
       <c r="B62" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7508,34 +7495,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555486</v>
+        <v>555272</v>
       </c>
       <c r="R62" t="n">
-        <v>6939852</v>
+        <v>6939241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7581,7 +7568,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7603,10 +7590,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215731</v>
+        <v>120215716</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7615,25 +7602,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7643,10 +7630,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555532</v>
+        <v>555321</v>
       </c>
       <c r="R63" t="n">
-        <v>6939560</v>
+        <v>6939670</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7692,7 +7679,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7714,10 +7701,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215666</v>
+        <v>120215702</v>
       </c>
       <c r="B64" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7726,25 +7713,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7754,10 +7741,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555418</v>
+        <v>555204</v>
       </c>
       <c r="R64" t="n">
-        <v>6939343</v>
+        <v>6939401</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7803,15 +7790,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7833,10 +7812,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215694</v>
+        <v>120215723</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,38 +7824,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555239</v>
+        <v>555369</v>
       </c>
       <c r="R65" t="n">
-        <v>6939322</v>
+        <v>6939717</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7922,7 +7905,15 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7944,10 +7935,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215710</v>
+        <v>120215665</v>
       </c>
       <c r="B66" t="n">
-        <v>89247</v>
+        <v>90416</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7956,38 +7947,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1596</v>
+        <v>6020</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555308</v>
+        <v>555444</v>
       </c>
       <c r="R66" t="n">
-        <v>6939650</v>
+        <v>6939356</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8033,7 +8024,15 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8055,10 +8054,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215672</v>
+        <v>120215735</v>
       </c>
       <c r="B67" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8071,34 +8070,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555256</v>
+        <v>555516</v>
       </c>
       <c r="R67" t="n">
-        <v>6939301</v>
+        <v>6939844</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8144,7 +8143,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8166,10 +8165,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215670</v>
+        <v>120215707</v>
       </c>
       <c r="B68" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8178,38 +8177,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555366</v>
+        <v>555227</v>
       </c>
       <c r="R68" t="n">
-        <v>6939325</v>
+        <v>6939530</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8255,7 +8254,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8277,10 +8276,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215708</v>
+        <v>120215695</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8293,34 +8292,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555296</v>
+        <v>555248</v>
       </c>
       <c r="R69" t="n">
-        <v>6939533</v>
+        <v>6939350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8366,7 +8365,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8388,7 +8387,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215735</v>
+        <v>120215684</v>
       </c>
       <c r="B70" t="n">
         <v>91858</v>
@@ -8424,14 +8423,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555516</v>
+        <v>555328</v>
       </c>
       <c r="R70" t="n">
-        <v>6939844</v>
+        <v>6939359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8477,7 +8476,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8499,10 +8498,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215738</v>
+        <v>120215680</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8515,34 +8514,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555480</v>
+        <v>555303</v>
       </c>
       <c r="R71" t="n">
-        <v>6939802</v>
+        <v>6939247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8588,7 +8587,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8610,10 +8614,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215696</v>
+        <v>120215742</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8626,34 +8630,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555200</v>
+        <v>555461</v>
       </c>
       <c r="R72" t="n">
-        <v>6939344</v>
+        <v>6939822</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8699,7 +8703,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8721,10 +8725,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215702</v>
+        <v>120215662</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8737,21 +8741,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8761,10 +8765,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555204</v>
+        <v>555210</v>
       </c>
       <c r="R73" t="n">
-        <v>6939401</v>
+        <v>6939191</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8810,7 +8814,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8832,7 +8836,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215678</v>
+        <v>120215686</v>
       </c>
       <c r="B74" t="n">
         <v>91858</v>
@@ -8872,10 +8876,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555271</v>
+        <v>555296</v>
       </c>
       <c r="R74" t="n">
-        <v>6939246</v>
+        <v>6939306</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8921,7 +8925,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8943,10 +8947,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215709</v>
+        <v>120215697</v>
       </c>
       <c r="B75" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8955,38 +8959,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555350</v>
+        <v>555218</v>
       </c>
       <c r="R75" t="n">
-        <v>6939568</v>
+        <v>6939369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9032,7 +9036,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9054,10 +9058,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215693</v>
+        <v>120215668</v>
       </c>
       <c r="B76" t="n">
-        <v>91850</v>
+        <v>79527</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9066,25 +9070,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9094,10 +9098,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555255</v>
+        <v>555394</v>
       </c>
       <c r="R76" t="n">
-        <v>6939329</v>
+        <v>6939336</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9143,7 +9147,15 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9165,10 +9177,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215669</v>
+        <v>120215715</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9177,38 +9189,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555391</v>
+        <v>555320</v>
       </c>
       <c r="R77" t="n">
-        <v>6939341</v>
+        <v>6939665</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9254,7 +9266,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9276,10 +9288,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215732</v>
+        <v>120215663</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9292,34 +9304,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555453</v>
+        <v>555335</v>
       </c>
       <c r="R78" t="n">
-        <v>6939688</v>
+        <v>6939295</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9365,7 +9377,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9387,10 +9399,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215743</v>
+        <v>120215741</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9399,25 +9411,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9427,10 +9439,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555438</v>
+        <v>555486</v>
       </c>
       <c r="R79" t="n">
-        <v>6939819</v>
+        <v>6939852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9476,7 +9488,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9498,10 +9510,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215723</v>
+        <v>120215683</v>
       </c>
       <c r="B80" t="n">
-        <v>91839</v>
+        <v>91874</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9510,42 +9522,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6055</v>
+        <v>2059</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555369</v>
+        <v>555323</v>
       </c>
       <c r="R80" t="n">
-        <v>6939717</v>
+        <v>6939333</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9591,15 +9599,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215717</v>
+        <v>120215710</v>
       </c>
       <c r="B81" t="n">
-        <v>78279</v>
+        <v>89247</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9633,25 +9633,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>1596</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555370</v>
+        <v>555308</v>
       </c>
       <c r="R81" t="n">
-        <v>6939656</v>
+        <v>6939650</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,15 +9710,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9740,7 +9732,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215684</v>
+        <v>120215725</v>
       </c>
       <c r="B82" t="n">
         <v>91858</v>
@@ -9776,14 +9768,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555328</v>
+        <v>555442</v>
       </c>
       <c r="R82" t="n">
-        <v>6939359</v>
+        <v>6939660</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9829,7 +9821,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9851,10 +9843,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215679</v>
+        <v>120215733</v>
       </c>
       <c r="B83" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9863,38 +9855,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555272</v>
+        <v>555508</v>
       </c>
       <c r="R83" t="n">
-        <v>6939241</v>
+        <v>6939693</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9940,7 +9932,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9962,10 +9954,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215676</v>
+        <v>120215693</v>
       </c>
       <c r="B84" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9974,25 +9966,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10002,10 +9994,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555303</v>
+        <v>555255</v>
       </c>
       <c r="R84" t="n">
-        <v>6939259</v>
+        <v>6939329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10051,7 +10043,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10073,7 +10065,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215720</v>
+        <v>120215730</v>
       </c>
       <c r="B85" t="n">
         <v>91858</v>
@@ -10113,10 +10105,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555385</v>
+        <v>555499</v>
       </c>
       <c r="R85" t="n">
-        <v>6939665</v>
+        <v>6939547</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10162,7 +10154,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10184,10 +10176,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215716</v>
+        <v>120215667</v>
       </c>
       <c r="B86" t="n">
-        <v>89247</v>
+        <v>91850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10196,38 +10188,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1596</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555321</v>
+        <v>555412</v>
       </c>
       <c r="R86" t="n">
-        <v>6939670</v>
+        <v>6939333</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10273,7 +10265,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10295,10 +10287,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215703</v>
+        <v>120215666</v>
       </c>
       <c r="B87" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10307,25 +10299,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10335,10 +10327,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555338</v>
+        <v>555418</v>
       </c>
       <c r="R87" t="n">
-        <v>6939447</v>
+        <v>6939343</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10384,7 +10376,15 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2413,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215673</v>
+        <v>120215705</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,25 +2425,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555256</v>
+        <v>555220</v>
       </c>
       <c r="R17" t="n">
-        <v>6939303</v>
+        <v>6939479</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215705</v>
+        <v>120215673</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,25 +2536,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555220</v>
+        <v>555256</v>
       </c>
       <c r="R18" t="n">
-        <v>6939479</v>
+        <v>6939303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215696</v>
+        <v>120215681</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,25 +2647,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555200</v>
+        <v>555310</v>
       </c>
       <c r="R19" t="n">
-        <v>6939344</v>
+        <v>6939320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2724,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2746,7 +2751,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215720</v>
+        <v>120215696</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2782,14 +2787,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555385</v>
+        <v>555200</v>
       </c>
       <c r="R20" t="n">
-        <v>6939665</v>
+        <v>6939344</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2840,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215664</v>
+        <v>120215720</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,38 +2874,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555450</v>
+        <v>555385</v>
       </c>
       <c r="R21" t="n">
-        <v>6939355</v>
+        <v>6939665</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2951,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2968,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215714</v>
+        <v>120215664</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,34 +2989,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555320</v>
+        <v>555450</v>
       </c>
       <c r="R22" t="n">
-        <v>6939663</v>
+        <v>6939355</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,15 +3062,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3087,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215732</v>
+        <v>120215714</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,25 +3096,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3127,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555453</v>
+        <v>555320</v>
       </c>
       <c r="R23" t="n">
-        <v>6939688</v>
+        <v>6939663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,7 +3173,15 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3198,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215681</v>
+        <v>120215732</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3210,38 +3215,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555310</v>
+        <v>555453</v>
       </c>
       <c r="R24" t="n">
-        <v>6939320</v>
+        <v>6939688</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,12 +3292,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215671</v>
+        <v>120215736</v>
       </c>
       <c r="B25" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,38 +3326,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555366</v>
+        <v>555530</v>
       </c>
       <c r="R25" t="n">
-        <v>6939325</v>
+        <v>6939888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215736</v>
+        <v>120215671</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3548,38 +3548,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555530</v>
+        <v>555366</v>
       </c>
       <c r="R27" t="n">
-        <v>6939888</v>
+        <v>6939325</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215728</v>
+        <v>120215678</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3659,38 +3659,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555484</v>
+        <v>555271</v>
       </c>
       <c r="R28" t="n">
-        <v>6939523</v>
+        <v>6939246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3736,12 +3736,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>körspår</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3763,10 +3758,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215678</v>
+        <v>120215728</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3775,38 +3770,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555271</v>
+        <v>555484</v>
       </c>
       <c r="R29" t="n">
-        <v>6939246</v>
+        <v>6939523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3852,7 +3847,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -6348,10 +6348,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215740</v>
+        <v>120215738</v>
       </c>
       <c r="B52" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6360,25 +6360,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555485</v>
+        <v>555480</v>
       </c>
       <c r="R52" t="n">
-        <v>6939841</v>
+        <v>6939802</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215738</v>
+        <v>120215740</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555480</v>
+        <v>555485</v>
       </c>
       <c r="R53" t="n">
-        <v>6939802</v>
+        <v>6939841</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215713</v>
+        <v>120215721</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555307</v>
+        <v>555389</v>
       </c>
       <c r="R54" t="n">
-        <v>6939679</v>
+        <v>6939706</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6659,7 +6659,15 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6681,10 +6689,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215722</v>
+        <v>120215717</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6693,25 +6701,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6721,10 +6729,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555358</v>
+        <v>555370</v>
       </c>
       <c r="R55" t="n">
-        <v>6939668</v>
+        <v>6939656</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6771,6 +6779,14 @@
       <c r="AI55" t="inlineStr">
         <is>
           <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6792,10 +6808,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215721</v>
+        <v>120215712</v>
       </c>
       <c r="B56" t="n">
-        <v>78279</v>
+        <v>90084</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6804,25 +6820,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>256703</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6832,10 +6848,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555389</v>
+        <v>555317</v>
       </c>
       <c r="R56" t="n">
-        <v>6939706</v>
+        <v>6939671</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6881,15 +6897,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6911,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215717</v>
+        <v>120215713</v>
       </c>
       <c r="B57" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6923,25 +6931,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6951,10 +6959,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555370</v>
+        <v>555307</v>
       </c>
       <c r="R57" t="n">
-        <v>6939656</v>
+        <v>6939679</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7000,15 +7008,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7030,10 +7030,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215712</v>
+        <v>120215722</v>
       </c>
       <c r="B58" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555317</v>
+        <v>555358</v>
       </c>
       <c r="R58" t="n">
-        <v>6939671</v>
+        <v>6939668</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215662</v>
+        <v>120215697</v>
       </c>
       <c r="B73" t="n">
-        <v>91870</v>
+        <v>89292</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8737,25 +8737,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555210</v>
+        <v>555218</v>
       </c>
       <c r="R73" t="n">
-        <v>6939191</v>
+        <v>6939369</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8836,10 +8836,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215686</v>
+        <v>120215668</v>
       </c>
       <c r="B74" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8852,21 +8852,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8876,10 +8876,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555296</v>
+        <v>555394</v>
       </c>
       <c r="R74" t="n">
-        <v>6939306</v>
+        <v>6939336</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8925,7 +8925,15 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8947,10 +8955,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215697</v>
+        <v>120215662</v>
       </c>
       <c r="B75" t="n">
-        <v>89292</v>
+        <v>91870</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8959,25 +8967,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8987,10 +8995,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555218</v>
+        <v>555210</v>
       </c>
       <c r="R75" t="n">
-        <v>6939369</v>
+        <v>6939191</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9036,7 +9044,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9058,10 +9066,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215668</v>
+        <v>120215686</v>
       </c>
       <c r="B76" t="n">
-        <v>79527</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9074,21 +9082,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9098,10 +9106,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555394</v>
+        <v>555296</v>
       </c>
       <c r="R76" t="n">
-        <v>6939336</v>
+        <v>6939306</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9147,15 +9155,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215741</v>
+        <v>120215683</v>
       </c>
       <c r="B79" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9415,34 +9415,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555486</v>
+        <v>555323</v>
       </c>
       <c r="R79" t="n">
-        <v>6939852</v>
+        <v>6939333</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9510,10 +9510,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215683</v>
+        <v>120215710</v>
       </c>
       <c r="B80" t="n">
-        <v>91874</v>
+        <v>89247</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9522,38 +9522,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>1596</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555323</v>
+        <v>555308</v>
       </c>
       <c r="R80" t="n">
-        <v>6939333</v>
+        <v>6939650</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215710</v>
+        <v>120215741</v>
       </c>
       <c r="B81" t="n">
-        <v>89247</v>
+        <v>91902</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9633,25 +9633,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1596</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555308</v>
+        <v>555486</v>
       </c>
       <c r="R81" t="n">
-        <v>6939650</v>
+        <v>6939852</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215694</v>
+        <v>120215731</v>
       </c>
       <c r="B15" t="n">
         <v>91858</v>
@@ -2219,14 +2219,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555239</v>
+        <v>555532</v>
       </c>
       <c r="R15" t="n">
-        <v>6939322</v>
+        <v>6939560</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215729</v>
+        <v>120215724</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555492</v>
+        <v>555408</v>
       </c>
       <c r="R16" t="n">
-        <v>6939553</v>
+        <v>6939701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,15 +2383,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2413,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215705</v>
+        <v>120215662</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,21 +2421,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2453,10 +2445,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555220</v>
+        <v>555210</v>
       </c>
       <c r="R17" t="n">
-        <v>6939479</v>
+        <v>6939191</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2494,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2524,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215673</v>
+        <v>120215720</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,38 +2528,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555256</v>
+        <v>555385</v>
       </c>
       <c r="R18" t="n">
-        <v>6939303</v>
+        <v>6939665</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2605,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2635,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215681</v>
+        <v>120215699</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>91874</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,21 +2643,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555310</v>
+        <v>555266</v>
       </c>
       <c r="R19" t="n">
-        <v>6939320</v>
+        <v>6939388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,12 +2716,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2751,7 +2738,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215696</v>
+        <v>120215686</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2791,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555200</v>
+        <v>555296</v>
       </c>
       <c r="R20" t="n">
-        <v>6939344</v>
+        <v>6939306</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2827,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2862,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215720</v>
+        <v>120215697</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,38 +2861,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555385</v>
+        <v>555218</v>
       </c>
       <c r="R21" t="n">
-        <v>6939665</v>
+        <v>6939369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2938,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215714</v>
+        <v>120215669</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,38 +3083,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555320</v>
+        <v>555391</v>
       </c>
       <c r="R23" t="n">
-        <v>6939663</v>
+        <v>6939341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,15 +3160,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3203,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215732</v>
+        <v>120215690</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,38 +3194,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555453</v>
+        <v>555293</v>
       </c>
       <c r="R24" t="n">
-        <v>6939688</v>
+        <v>6939349</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3292,7 +3271,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3314,10 +3293,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215736</v>
+        <v>120215742</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3330,21 +3309,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3354,10 +3333,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555530</v>
+        <v>555461</v>
       </c>
       <c r="R25" t="n">
-        <v>6939888</v>
+        <v>6939822</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3425,10 +3404,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215706</v>
+        <v>120215721</v>
       </c>
       <c r="B26" t="n">
-        <v>91481</v>
+        <v>78279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,34 +3420,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555195</v>
+        <v>555389</v>
       </c>
       <c r="R26" t="n">
-        <v>6939463</v>
+        <v>6939706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,7 +3493,15 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3536,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215671</v>
+        <v>120215740</v>
       </c>
       <c r="B27" t="n">
-        <v>91874</v>
+        <v>89292</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3548,38 +3535,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555366</v>
+        <v>555485</v>
       </c>
       <c r="R27" t="n">
-        <v>6939325</v>
+        <v>6939841</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3625,7 +3612,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3647,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215678</v>
+        <v>120215741</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3659,38 +3646,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555271</v>
+        <v>555486</v>
       </c>
       <c r="R28" t="n">
-        <v>6939246</v>
+        <v>6939852</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3736,7 +3723,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3758,10 +3745,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215728</v>
+        <v>120215692</v>
       </c>
       <c r="B29" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,38 +3757,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555484</v>
+        <v>555260</v>
       </c>
       <c r="R29" t="n">
-        <v>6939523</v>
+        <v>6939329</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3847,12 +3834,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>körspår</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3874,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215709</v>
+        <v>120215715</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3886,25 +3868,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3914,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555350</v>
+        <v>555320</v>
       </c>
       <c r="R30" t="n">
-        <v>6939568</v>
+        <v>6939665</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3945,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3985,10 +3967,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215687</v>
+        <v>120215672</v>
       </c>
       <c r="B31" t="n">
-        <v>78279</v>
+        <v>90084</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3997,25 +3979,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>256703</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4025,10 +4007,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555260</v>
+        <v>555256</v>
       </c>
       <c r="R31" t="n">
-        <v>6939288</v>
+        <v>6939301</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4074,15 +4056,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4104,10 +4078,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215731</v>
+        <v>120215706</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4116,38 +4090,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555532</v>
+        <v>555195</v>
       </c>
       <c r="R32" t="n">
-        <v>6939560</v>
+        <v>6939463</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4193,7 +4167,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4215,10 +4189,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215743</v>
+        <v>120215681</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4227,38 +4201,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555438</v>
+        <v>555310</v>
       </c>
       <c r="R33" t="n">
-        <v>6939819</v>
+        <v>6939320</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4304,7 +4278,12 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4326,7 +4305,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215670</v>
+        <v>120215679</v>
       </c>
       <c r="B34" t="n">
         <v>91850</v>
@@ -4366,10 +4345,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555366</v>
+        <v>555272</v>
       </c>
       <c r="R34" t="n">
-        <v>6939325</v>
+        <v>6939241</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4415,7 +4394,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4437,10 +4416,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215704</v>
+        <v>120215736</v>
       </c>
       <c r="B35" t="n">
-        <v>91328</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4449,38 +4428,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555333</v>
+        <v>555530</v>
       </c>
       <c r="R35" t="n">
-        <v>6939465</v>
+        <v>6939888</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4526,7 +4505,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4548,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215688</v>
+        <v>120215708</v>
       </c>
       <c r="B36" t="n">
-        <v>90848</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4560,38 +4539,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555246</v>
+        <v>555296</v>
       </c>
       <c r="R36" t="n">
-        <v>6939300</v>
+        <v>6939533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4637,15 +4616,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4667,10 +4638,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215676</v>
+        <v>120215711</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,38 +4650,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555303</v>
+        <v>555311</v>
       </c>
       <c r="R37" t="n">
-        <v>6939259</v>
+        <v>6939662</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4756,7 +4727,12 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4778,10 +4754,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215726</v>
+        <v>120215713</v>
       </c>
       <c r="B38" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4790,25 +4766,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4818,10 +4794,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555445</v>
+        <v>555307</v>
       </c>
       <c r="R38" t="n">
-        <v>6939653</v>
+        <v>6939679</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,7 +4843,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4889,10 +4865,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215719</v>
+        <v>120215687</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4901,38 +4877,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555393</v>
+        <v>555260</v>
       </c>
       <c r="R39" t="n">
-        <v>6939610</v>
+        <v>6939288</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4978,7 +4954,15 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5000,7 +4984,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215703</v>
+        <v>120215691</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5040,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555338</v>
+        <v>555287</v>
       </c>
       <c r="R40" t="n">
-        <v>6939447</v>
+        <v>6939378</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5089,7 +5073,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5111,10 +5095,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215682</v>
+        <v>120215678</v>
       </c>
       <c r="B41" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5123,25 +5107,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5151,10 +5135,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555325</v>
+        <v>555271</v>
       </c>
       <c r="R41" t="n">
-        <v>6939312</v>
+        <v>6939246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5200,7 +5184,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5222,10 +5206,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215675</v>
+        <v>120215683</v>
       </c>
       <c r="B42" t="n">
-        <v>92048</v>
+        <v>91874</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5238,21 +5222,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5262,10 +5246,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555371</v>
+        <v>555323</v>
       </c>
       <c r="R42" t="n">
-        <v>6939272</v>
+        <v>6939333</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5311,15 +5295,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5341,10 +5317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215674</v>
+        <v>120215668</v>
       </c>
       <c r="B43" t="n">
-        <v>91042</v>
+        <v>79527</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,25 +5329,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5467</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5381,10 +5357,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555331</v>
+        <v>555394</v>
       </c>
       <c r="R43" t="n">
-        <v>6939284</v>
+        <v>6939336</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5430,7 +5406,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5438,7 +5414,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5460,10 +5436,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215690</v>
+        <v>120215728</v>
       </c>
       <c r="B44" t="n">
-        <v>91901</v>
+        <v>91850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5476,34 +5452,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555293</v>
+        <v>555484</v>
       </c>
       <c r="R44" t="n">
-        <v>6939349</v>
+        <v>6939523</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5549,7 +5525,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5571,10 +5552,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215699</v>
+        <v>120215707</v>
       </c>
       <c r="B45" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5583,38 +5564,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555266</v>
+        <v>555227</v>
       </c>
       <c r="R45" t="n">
-        <v>6939388</v>
+        <v>6939530</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5660,7 +5641,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5682,7 +5663,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215727</v>
+        <v>120215719</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5722,10 +5703,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555438</v>
+        <v>555393</v>
       </c>
       <c r="R46" t="n">
-        <v>6939535</v>
+        <v>6939610</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5771,7 +5752,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5793,7 +5774,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215708</v>
+        <v>120215732</v>
       </c>
       <c r="B47" t="n">
         <v>91858</v>
@@ -5833,10 +5814,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555296</v>
+        <v>555453</v>
       </c>
       <c r="R47" t="n">
-        <v>6939533</v>
+        <v>6939688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5882,7 +5863,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5904,10 +5885,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120215692</v>
+        <v>120215688</v>
       </c>
       <c r="B48" t="n">
-        <v>89292</v>
+        <v>90848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,25 +5897,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6286</v>
+        <v>71</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5925,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555260</v>
+        <v>555246</v>
       </c>
       <c r="R48" t="n">
-        <v>6939329</v>
+        <v>6939300</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5993,7 +5974,15 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6015,7 +6004,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215669</v>
+        <v>120215696</v>
       </c>
       <c r="B49" t="n">
         <v>91858</v>
@@ -6055,10 +6044,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555391</v>
+        <v>555200</v>
       </c>
       <c r="R49" t="n">
-        <v>6939341</v>
+        <v>6939344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6104,7 +6093,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6126,10 +6115,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215724</v>
+        <v>120215695</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6142,34 +6131,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555408</v>
+        <v>555248</v>
       </c>
       <c r="R50" t="n">
-        <v>6939701</v>
+        <v>6939350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6215,7 +6204,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6237,10 +6226,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215691</v>
+        <v>120215726</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6249,38 +6238,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555287</v>
+        <v>555445</v>
       </c>
       <c r="R51" t="n">
-        <v>6939378</v>
+        <v>6939653</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6326,7 +6315,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6348,10 +6337,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215738</v>
+        <v>120215704</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6360,38 +6349,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555480</v>
+        <v>555333</v>
       </c>
       <c r="R52" t="n">
-        <v>6939802</v>
+        <v>6939465</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,7 +6426,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6459,10 +6448,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215740</v>
+        <v>120215729</v>
       </c>
       <c r="B53" t="n">
-        <v>89292</v>
+        <v>79160</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6471,25 +6460,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6286</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6499,10 +6488,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555485</v>
+        <v>555492</v>
       </c>
       <c r="R53" t="n">
-        <v>6939841</v>
+        <v>6939553</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6548,7 +6537,15 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6570,10 +6567,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215721</v>
+        <v>120215694</v>
       </c>
       <c r="B54" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6582,38 +6579,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555389</v>
+        <v>555239</v>
       </c>
       <c r="R54" t="n">
-        <v>6939706</v>
+        <v>6939322</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6659,15 +6656,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6689,10 +6678,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215717</v>
+        <v>120215727</v>
       </c>
       <c r="B55" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6701,25 +6690,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6729,10 +6718,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555370</v>
+        <v>555438</v>
       </c>
       <c r="R55" t="n">
-        <v>6939656</v>
+        <v>6939535</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6778,15 +6767,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6808,10 +6789,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215712</v>
+        <v>120215743</v>
       </c>
       <c r="B56" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6824,21 +6805,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6848,10 +6829,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555317</v>
+        <v>555438</v>
       </c>
       <c r="R56" t="n">
-        <v>6939671</v>
+        <v>6939819</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6897,7 +6878,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6919,7 +6900,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215713</v>
+        <v>120215703</v>
       </c>
       <c r="B57" t="n">
         <v>91858</v>
@@ -6955,14 +6936,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555307</v>
+        <v>555338</v>
       </c>
       <c r="R57" t="n">
-        <v>6939679</v>
+        <v>6939447</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7008,7 +6989,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7030,7 +7011,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215722</v>
+        <v>120215709</v>
       </c>
       <c r="B58" t="n">
         <v>91858</v>
@@ -7070,10 +7051,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555358</v>
+        <v>555350</v>
       </c>
       <c r="R58" t="n">
-        <v>6939668</v>
+        <v>6939568</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7141,10 +7122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215672</v>
+        <v>120215723</v>
       </c>
       <c r="B59" t="n">
-        <v>90084</v>
+        <v>91839</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7153,38 +7134,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>256703</v>
+        <v>6055</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555256</v>
+        <v>555369</v>
       </c>
       <c r="R59" t="n">
-        <v>6939301</v>
+        <v>6939717</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7230,7 +7215,15 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7252,10 +7245,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215677</v>
+        <v>120215716</v>
       </c>
       <c r="B60" t="n">
-        <v>90084</v>
+        <v>89247</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7264,38 +7257,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>256703</v>
+        <v>1596</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555282</v>
+        <v>555321</v>
       </c>
       <c r="R60" t="n">
-        <v>6939236</v>
+        <v>6939670</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7341,7 +7334,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7363,10 +7356,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215711</v>
+        <v>120215675</v>
       </c>
       <c r="B61" t="n">
-        <v>91904</v>
+        <v>92048</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7375,38 +7368,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>232140</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555311</v>
+        <v>555371</v>
       </c>
       <c r="R61" t="n">
-        <v>6939662</v>
+        <v>6939272</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7452,12 +7445,15 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN61" t="n">
+        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>under gammal tallågerest</t>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7479,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215679</v>
+        <v>120215666</v>
       </c>
       <c r="B62" t="n">
-        <v>91850</v>
+        <v>91839</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7491,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4361</v>
+        <v>6055</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7519,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555272</v>
+        <v>555418</v>
       </c>
       <c r="R62" t="n">
-        <v>6939241</v>
+        <v>6939343</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7568,7 +7564,15 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7590,10 +7594,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215716</v>
+        <v>120215682</v>
       </c>
       <c r="B63" t="n">
-        <v>89247</v>
+        <v>91874</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7602,38 +7606,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1596</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555321</v>
+        <v>555325</v>
       </c>
       <c r="R63" t="n">
-        <v>6939670</v>
+        <v>6939312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7679,7 +7683,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7812,10 +7816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215723</v>
+        <v>120215730</v>
       </c>
       <c r="B65" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7824,42 +7828,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555369</v>
+        <v>555499</v>
       </c>
       <c r="R65" t="n">
-        <v>6939717</v>
+        <v>6939547</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7905,15 +7905,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7935,10 +7927,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215665</v>
+        <v>120215676</v>
       </c>
       <c r="B66" t="n">
-        <v>90416</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7947,25 +7939,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6020</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7975,10 +7967,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555444</v>
+        <v>555303</v>
       </c>
       <c r="R66" t="n">
-        <v>6939356</v>
+        <v>6939259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8024,15 +8016,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8054,10 +8038,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215735</v>
+        <v>120215670</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8066,38 +8050,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555516</v>
+        <v>555366</v>
       </c>
       <c r="R67" t="n">
-        <v>6939844</v>
+        <v>6939325</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8143,7 +8127,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8165,10 +8149,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215707</v>
+        <v>120215677</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8181,34 +8165,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555227</v>
+        <v>555282</v>
       </c>
       <c r="R68" t="n">
-        <v>6939530</v>
+        <v>6939236</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8254,7 +8238,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8276,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215695</v>
+        <v>120215725</v>
       </c>
       <c r="B69" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8292,34 +8276,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555248</v>
+        <v>555442</v>
       </c>
       <c r="R69" t="n">
-        <v>6939350</v>
+        <v>6939660</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8365,7 +8349,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8387,10 +8371,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215684</v>
+        <v>120215667</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8399,25 +8383,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8427,10 +8411,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555328</v>
+        <v>555412</v>
       </c>
       <c r="R70" t="n">
-        <v>6939359</v>
+        <v>6939333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8476,7 +8460,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8498,10 +8482,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215680</v>
+        <v>120215693</v>
       </c>
       <c r="B71" t="n">
-        <v>90545</v>
+        <v>91850</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8510,25 +8494,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8538,10 +8522,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555303</v>
+        <v>555255</v>
       </c>
       <c r="R71" t="n">
-        <v>6939247</v>
+        <v>6939329</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8587,12 +8571,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8614,10 +8593,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215742</v>
+        <v>120215722</v>
       </c>
       <c r="B72" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8630,21 +8609,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8654,10 +8633,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555461</v>
+        <v>555358</v>
       </c>
       <c r="R72" t="n">
-        <v>6939822</v>
+        <v>6939668</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8703,7 +8682,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8725,10 +8704,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215697</v>
+        <v>120215663</v>
       </c>
       <c r="B73" t="n">
-        <v>89292</v>
+        <v>91870</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8737,25 +8716,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8765,10 +8744,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555218</v>
+        <v>555335</v>
       </c>
       <c r="R73" t="n">
-        <v>6939369</v>
+        <v>6939295</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8814,7 +8793,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8836,10 +8815,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215668</v>
+        <v>120215674</v>
       </c>
       <c r="B74" t="n">
-        <v>79527</v>
+        <v>91042</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8848,25 +8827,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>5467</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8876,10 +8855,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555394</v>
+        <v>555331</v>
       </c>
       <c r="R74" t="n">
-        <v>6939336</v>
+        <v>6939284</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8925,7 +8904,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
         </is>
       </c>
       <c r="AN74" t="n">
@@ -8933,7 +8912,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8955,10 +8934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215662</v>
+        <v>120215673</v>
       </c>
       <c r="B75" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8967,25 +8946,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8995,10 +8974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555210</v>
+        <v>555256</v>
       </c>
       <c r="R75" t="n">
-        <v>6939191</v>
+        <v>6939303</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9044,7 +9023,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9066,7 +9045,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215686</v>
+        <v>120215705</v>
       </c>
       <c r="B76" t="n">
         <v>91858</v>
@@ -9106,10 +9085,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555296</v>
+        <v>555220</v>
       </c>
       <c r="R76" t="n">
-        <v>6939306</v>
+        <v>6939479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9155,7 +9134,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9177,10 +9156,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215715</v>
+        <v>120215710</v>
       </c>
       <c r="B77" t="n">
-        <v>91328</v>
+        <v>89247</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9193,21 +9172,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1958</v>
+        <v>1596</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9217,10 +9196,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555320</v>
+        <v>555308</v>
       </c>
       <c r="R77" t="n">
-        <v>6939665</v>
+        <v>6939650</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9266,7 +9245,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9288,10 +9267,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215663</v>
+        <v>120215680</v>
       </c>
       <c r="B78" t="n">
-        <v>91870</v>
+        <v>90545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9304,21 +9283,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9328,10 +9307,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555335</v>
+        <v>555303</v>
       </c>
       <c r="R78" t="n">
-        <v>6939295</v>
+        <v>6939247</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9377,7 +9356,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9399,10 +9383,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215683</v>
+        <v>120215712</v>
       </c>
       <c r="B79" t="n">
-        <v>91874</v>
+        <v>90084</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9411,38 +9395,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555323</v>
+        <v>555317</v>
       </c>
       <c r="R79" t="n">
-        <v>6939333</v>
+        <v>6939671</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9488,7 +9472,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9510,10 +9494,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215710</v>
+        <v>120215738</v>
       </c>
       <c r="B80" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9522,25 +9506,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9550,10 +9534,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555308</v>
+        <v>555480</v>
       </c>
       <c r="R80" t="n">
-        <v>6939650</v>
+        <v>6939802</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9599,7 +9583,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9621,10 +9605,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215741</v>
+        <v>120215717</v>
       </c>
       <c r="B81" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9637,21 +9621,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9661,10 +9645,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555486</v>
+        <v>555370</v>
       </c>
       <c r="R81" t="n">
-        <v>6939852</v>
+        <v>6939656</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,7 +9694,15 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9732,7 +9724,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215725</v>
+        <v>120215684</v>
       </c>
       <c r="B82" t="n">
         <v>91858</v>
@@ -9768,14 +9760,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555442</v>
+        <v>555328</v>
       </c>
       <c r="R82" t="n">
-        <v>6939660</v>
+        <v>6939359</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9821,7 +9813,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9843,10 +9835,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215733</v>
+        <v>120215671</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9855,38 +9847,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555508</v>
+        <v>555366</v>
       </c>
       <c r="R83" t="n">
-        <v>6939693</v>
+        <v>6939325</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9932,7 +9924,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9954,10 +9946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215693</v>
+        <v>120215735</v>
       </c>
       <c r="B84" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9966,38 +9958,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555255</v>
+        <v>555516</v>
       </c>
       <c r="R84" t="n">
-        <v>6939329</v>
+        <v>6939844</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,7 +10035,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10065,7 +10057,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215730</v>
+        <v>120215733</v>
       </c>
       <c r="B85" t="n">
         <v>91858</v>
@@ -10105,10 +10097,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555499</v>
+        <v>555508</v>
       </c>
       <c r="R85" t="n">
-        <v>6939547</v>
+        <v>6939693</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10154,7 +10146,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10176,10 +10168,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215667</v>
+        <v>120215714</v>
       </c>
       <c r="B86" t="n">
-        <v>91850</v>
+        <v>78187</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10192,34 +10184,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555412</v>
+        <v>555320</v>
       </c>
       <c r="R86" t="n">
-        <v>6939333</v>
+        <v>6939663</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10265,7 +10257,15 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10287,10 +10287,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215666</v>
+        <v>120215665</v>
       </c>
       <c r="B87" t="n">
-        <v>91839</v>
+        <v>90416</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10299,25 +10299,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6055</v>
+        <v>6020</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10327,10 +10327,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555418</v>
+        <v>555444</v>
       </c>
       <c r="R87" t="n">
-        <v>6939343</v>
+        <v>6939356</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215731</v>
+        <v>120215729</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555532</v>
+        <v>555492</v>
       </c>
       <c r="R15" t="n">
-        <v>6939560</v>
+        <v>6939553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2294,7 +2302,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215724</v>
+        <v>120215709</v>
       </c>
       <c r="B16" t="n">
         <v>91858</v>
@@ -2334,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555408</v>
+        <v>555350</v>
       </c>
       <c r="R16" t="n">
-        <v>6939701</v>
+        <v>6939568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2391,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120215662</v>
+        <v>120215687</v>
       </c>
       <c r="B17" t="n">
-        <v>91870</v>
+        <v>78279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,25 +2425,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2445,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555210</v>
+        <v>555260</v>
       </c>
       <c r="R17" t="n">
-        <v>6939191</v>
+        <v>6939288</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2502,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2516,7 +2532,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120215720</v>
+        <v>120215724</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2556,10 +2572,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555385</v>
+        <v>555408</v>
       </c>
       <c r="R18" t="n">
-        <v>6939665</v>
+        <v>6939701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2621,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>krön i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2627,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120215699</v>
+        <v>120215696</v>
       </c>
       <c r="B19" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,25 +2655,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2667,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555266</v>
+        <v>555200</v>
       </c>
       <c r="R19" t="n">
-        <v>6939388</v>
+        <v>6939344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2732,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2738,7 +2754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120215686</v>
+        <v>120215676</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2778,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555296</v>
+        <v>555303</v>
       </c>
       <c r="R20" t="n">
-        <v>6939306</v>
+        <v>6939259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,7 +2843,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2849,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120215697</v>
+        <v>120215678</v>
       </c>
       <c r="B21" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,25 +2877,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2889,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555218</v>
+        <v>555271</v>
       </c>
       <c r="R21" t="n">
-        <v>6939369</v>
+        <v>6939246</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2954,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2960,10 +2976,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120215664</v>
+        <v>120215674</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>91042</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,21 +2992,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3000,10 +3016,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555450</v>
+        <v>555331</v>
       </c>
       <c r="R22" t="n">
-        <v>6939355</v>
+        <v>6939284</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3065,15 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog i sydostvänd nipa</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3071,10 +3095,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120215669</v>
+        <v>120215692</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3083,25 +3107,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3111,10 +3135,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555391</v>
+        <v>555260</v>
       </c>
       <c r="R23" t="n">
-        <v>6939341</v>
+        <v>6939329</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3160,7 +3184,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3182,10 +3206,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215690</v>
+        <v>120215736</v>
       </c>
       <c r="B24" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3194,38 +3218,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555293</v>
+        <v>555530</v>
       </c>
       <c r="R24" t="n">
-        <v>6939349</v>
+        <v>6939888</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3271,7 +3295,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3293,10 +3317,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215742</v>
+        <v>120215668</v>
       </c>
       <c r="B25" t="n">
-        <v>90084</v>
+        <v>79527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3309,34 +3333,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>256703</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555461</v>
+        <v>555394</v>
       </c>
       <c r="R25" t="n">
-        <v>6939822</v>
+        <v>6939336</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3382,7 +3406,15 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3404,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215721</v>
+        <v>120215726</v>
       </c>
       <c r="B26" t="n">
-        <v>78279</v>
+        <v>91881</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3420,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3444,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555389</v>
+        <v>555445</v>
       </c>
       <c r="R26" t="n">
-        <v>6939706</v>
+        <v>6939653</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3493,15 +3525,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3523,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215740</v>
+        <v>120215682</v>
       </c>
       <c r="B27" t="n">
-        <v>89292</v>
+        <v>91874</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,38 +3559,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555485</v>
+        <v>555325</v>
       </c>
       <c r="R27" t="n">
-        <v>6939841</v>
+        <v>6939312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,7 +3636,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3634,10 +3658,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120215741</v>
+        <v>120215695</v>
       </c>
       <c r="B28" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,38 +3670,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555486</v>
+        <v>555248</v>
       </c>
       <c r="R28" t="n">
-        <v>6939852</v>
+        <v>6939350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3723,7 +3747,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3745,10 +3769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120215692</v>
+        <v>120215733</v>
       </c>
       <c r="B29" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3757,38 +3781,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555260</v>
+        <v>555508</v>
       </c>
       <c r="R29" t="n">
-        <v>6939329</v>
+        <v>6939693</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,7 +3858,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3856,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120215715</v>
+        <v>120215728</v>
       </c>
       <c r="B30" t="n">
-        <v>91328</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3868,25 +3892,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1958</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555320</v>
+        <v>555484</v>
       </c>
       <c r="R30" t="n">
-        <v>6939665</v>
+        <v>6939523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3945,7 +3969,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>körspår</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3967,7 +3996,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120215672</v>
+        <v>120215742</v>
       </c>
       <c r="B31" t="n">
         <v>90084</v>
@@ -4003,14 +4032,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555256</v>
+        <v>555461</v>
       </c>
       <c r="R31" t="n">
-        <v>6939301</v>
+        <v>6939822</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4056,7 +4085,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4078,10 +4107,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120215706</v>
+        <v>120215690</v>
       </c>
       <c r="B32" t="n">
-        <v>91481</v>
+        <v>91901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4094,34 +4123,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4745</v>
+        <v>5448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555195</v>
+        <v>555293</v>
       </c>
       <c r="R32" t="n">
-        <v>6939463</v>
+        <v>6939349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4167,7 +4196,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>under gran i 140-årig sandtallskog med väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4189,10 +4218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120215681</v>
+        <v>120215680</v>
       </c>
       <c r="B33" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,25 +4230,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4229,10 +4258,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555310</v>
+        <v>555303</v>
       </c>
       <c r="R33" t="n">
-        <v>6939320</v>
+        <v>6939247</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4283,7 +4312,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>omkullrasad brandstubbe</t>
+          <t>gammal tallågerest medkolade ytor</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4305,10 +4334,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120215679</v>
+        <v>120215694</v>
       </c>
       <c r="B34" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4317,25 +4346,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4345,10 +4374,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555272</v>
+        <v>555239</v>
       </c>
       <c r="R34" t="n">
-        <v>6939241</v>
+        <v>6939322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4394,7 +4423,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4416,10 +4445,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120215736</v>
+        <v>120215740</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4428,25 +4457,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4456,10 +4485,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555530</v>
+        <v>555485</v>
       </c>
       <c r="R35" t="n">
-        <v>6939888</v>
+        <v>6939841</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4534,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4527,10 +4556,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120215708</v>
+        <v>120215662</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4543,34 +4572,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555296</v>
+        <v>555210</v>
       </c>
       <c r="R36" t="n">
-        <v>6939533</v>
+        <v>6939191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4616,7 +4645,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4638,10 +4667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120215711</v>
+        <v>120215702</v>
       </c>
       <c r="B37" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4650,38 +4679,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555311</v>
+        <v>555204</v>
       </c>
       <c r="R37" t="n">
-        <v>6939662</v>
+        <v>6939401</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,12 +4756,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>under gammal tallågerest</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4754,7 +4778,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120215713</v>
+        <v>120215720</v>
       </c>
       <c r="B38" t="n">
         <v>91858</v>
@@ -4794,10 +4818,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555307</v>
+        <v>555385</v>
       </c>
       <c r="R38" t="n">
-        <v>6939679</v>
+        <v>6939665</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4843,7 +4867,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4865,10 +4889,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120215687</v>
+        <v>120215741</v>
       </c>
       <c r="B39" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4881,34 +4905,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555260</v>
+        <v>555486</v>
       </c>
       <c r="R39" t="n">
-        <v>6939288</v>
+        <v>6939852</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4954,15 +4978,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal brandhögstubbe</t>
+          <t>150-årig sandtallskogssluttning med spridd 200-årig tall</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4984,7 +5000,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120215691</v>
+        <v>120215684</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5024,10 +5040,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555287</v>
+        <v>555328</v>
       </c>
       <c r="R40" t="n">
-        <v>6939378</v>
+        <v>6939359</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5073,7 +5089,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5095,7 +5111,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120215678</v>
+        <v>120215722</v>
       </c>
       <c r="B41" t="n">
         <v>91858</v>
@@ -5131,14 +5147,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555271</v>
+        <v>555358</v>
       </c>
       <c r="R41" t="n">
-        <v>6939246</v>
+        <v>6939668</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5184,7 +5200,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5206,10 +5222,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120215683</v>
+        <v>120215679</v>
       </c>
       <c r="B42" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5222,21 +5238,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5246,10 +5262,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555323</v>
+        <v>555272</v>
       </c>
       <c r="R42" t="n">
-        <v>6939333</v>
+        <v>6939241</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5295,7 +5311,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5317,10 +5333,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120215668</v>
+        <v>120215699</v>
       </c>
       <c r="B43" t="n">
-        <v>79527</v>
+        <v>91874</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5329,25 +5345,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5357,10 +5373,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555394</v>
+        <v>555266</v>
       </c>
       <c r="R43" t="n">
-        <v>6939336</v>
+        <v>6939388</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,15 +5422,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5436,10 +5444,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120215728</v>
+        <v>120215681</v>
       </c>
       <c r="B44" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5452,34 +5460,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555484</v>
+        <v>555310</v>
       </c>
       <c r="R44" t="n">
-        <v>6939523</v>
+        <v>6939320</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5525,12 +5533,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>körspår</t>
+          <t>omkullrasad brandstubbe</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5552,10 +5560,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120215707</v>
+        <v>120215666</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5564,38 +5572,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555227</v>
+        <v>555418</v>
       </c>
       <c r="R45" t="n">
-        <v>6939530</v>
+        <v>6939343</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5641,7 +5649,15 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under grov marknära tallåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5663,10 +5679,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120215719</v>
+        <v>120215665</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>90416</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5675,38 +5691,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6020</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555393</v>
+        <v>555444</v>
       </c>
       <c r="R46" t="n">
-        <v>6939610</v>
+        <v>6939356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5752,7 +5768,15 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5774,7 +5798,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120215732</v>
+        <v>120215727</v>
       </c>
       <c r="B47" t="n">
         <v>91858</v>
@@ -5814,10 +5838,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555453</v>
+        <v>555438</v>
       </c>
       <c r="R47" t="n">
-        <v>6939688</v>
+        <v>6939535</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5863,7 +5887,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5885,10 +5909,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120215688</v>
+        <v>120215708</v>
       </c>
       <c r="B48" t="n">
-        <v>90848</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5897,38 +5921,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555246</v>
+        <v>555296</v>
       </c>
       <c r="R48" t="n">
-        <v>6939300</v>
+        <v>6939533</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,15 +5998,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>150-årig sandtallskog med lavfläckar i NV-sluttning</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6004,10 +6020,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120215696</v>
+        <v>120215710</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6016,38 +6032,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555200</v>
+        <v>555308</v>
       </c>
       <c r="R49" t="n">
-        <v>6939344</v>
+        <v>6939650</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6093,7 +6109,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och gråalsbuskar</t>
+          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6115,10 +6131,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120215695</v>
+        <v>120215669</v>
       </c>
       <c r="B50" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6131,21 +6147,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6155,10 +6171,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555248</v>
+        <v>555391</v>
       </c>
       <c r="R50" t="n">
-        <v>6939350</v>
+        <v>6939341</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6204,7 +6220,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6226,10 +6242,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120215726</v>
+        <v>120215732</v>
       </c>
       <c r="B51" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6238,25 +6254,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6266,10 +6282,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555445</v>
+        <v>555453</v>
       </c>
       <c r="R51" t="n">
-        <v>6939653</v>
+        <v>6939688</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6315,7 +6331,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6337,10 +6353,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215704</v>
+        <v>120215688</v>
       </c>
       <c r="B52" t="n">
-        <v>91328</v>
+        <v>90848</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6349,25 +6365,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1958</v>
+        <v>71</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6377,10 +6393,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555333</v>
+        <v>555246</v>
       </c>
       <c r="R52" t="n">
-        <v>6939465</v>
+        <v>6939300</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6426,7 +6442,15 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6448,10 +6472,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215729</v>
+        <v>120215706</v>
       </c>
       <c r="B53" t="n">
-        <v>79160</v>
+        <v>91481</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6464,34 +6488,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>4745</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555492</v>
+        <v>555195</v>
       </c>
       <c r="R53" t="n">
-        <v>6939553</v>
+        <v>6939463</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6537,15 +6561,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6567,7 +6583,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215694</v>
+        <v>120215738</v>
       </c>
       <c r="B54" t="n">
         <v>91858</v>
@@ -6603,14 +6619,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555239</v>
+        <v>555480</v>
       </c>
       <c r="R54" t="n">
-        <v>6939322</v>
+        <v>6939802</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6656,7 +6672,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i sydslänt</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6678,10 +6694,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120215727</v>
+        <v>120215716</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6690,25 +6706,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6718,10 +6734,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555438</v>
+        <v>555321</v>
       </c>
       <c r="R55" t="n">
-        <v>6939535</v>
+        <v>6939670</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6767,7 +6783,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>vindfällerensad 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6789,7 +6805,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215743</v>
+        <v>120215731</v>
       </c>
       <c r="B56" t="n">
         <v>91858</v>
@@ -6829,10 +6845,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555438</v>
+        <v>555532</v>
       </c>
       <c r="R56" t="n">
-        <v>6939819</v>
+        <v>6939560</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6878,7 +6894,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssluttning</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6900,10 +6916,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215703</v>
+        <v>120215664</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6912,25 +6928,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6940,10 +6956,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555338</v>
+        <v>555450</v>
       </c>
       <c r="R57" t="n">
-        <v>6939447</v>
+        <v>6939355</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6989,7 +7005,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7011,10 +7027,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215709</v>
+        <v>120215677</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7027,34 +7043,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555350</v>
+        <v>555282</v>
       </c>
       <c r="R58" t="n">
-        <v>6939568</v>
+        <v>6939236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7100,7 +7116,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7122,10 +7138,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215723</v>
+        <v>120215697</v>
       </c>
       <c r="B59" t="n">
-        <v>91839</v>
+        <v>89292</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7138,38 +7154,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6055</v>
+        <v>6286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555369</v>
+        <v>555218</v>
       </c>
       <c r="R59" t="n">
-        <v>6939717</v>
+        <v>6939369</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7215,15 +7227,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7245,10 +7249,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215716</v>
+        <v>120215667</v>
       </c>
       <c r="B60" t="n">
-        <v>89247</v>
+        <v>91850</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7257,38 +7261,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1596</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555321</v>
+        <v>555412</v>
       </c>
       <c r="R60" t="n">
-        <v>6939670</v>
+        <v>6939333</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7334,7 +7338,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7356,10 +7360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215675</v>
+        <v>120215713</v>
       </c>
       <c r="B61" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7368,38 +7372,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555371</v>
+        <v>555307</v>
       </c>
       <c r="R61" t="n">
-        <v>6939272</v>
+        <v>6939679</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7445,15 +7449,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7475,10 +7471,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120215666</v>
+        <v>120215725</v>
       </c>
       <c r="B62" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,38 +7483,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555418</v>
+        <v>555442</v>
       </c>
       <c r="R62" t="n">
-        <v>6939343</v>
+        <v>6939660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7564,15 +7560,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under grov marknära tallåga</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7594,10 +7582,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120215682</v>
+        <v>120215705</v>
       </c>
       <c r="B63" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7606,25 +7594,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7634,10 +7622,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555325</v>
+        <v>555220</v>
       </c>
       <c r="R63" t="n">
-        <v>6939312</v>
+        <v>6939479</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7683,7 +7671,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7705,7 +7693,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120215702</v>
+        <v>120215707</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7741,14 +7729,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555204</v>
+        <v>555227</v>
       </c>
       <c r="R64" t="n">
-        <v>6939401</v>
+        <v>6939530</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7794,7 +7782,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>140-årig sandtallskog med lavfläckar i NV-sluttning, nära tjärn</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7816,10 +7804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120215730</v>
+        <v>120215683</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7828,38 +7816,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555499</v>
+        <v>555323</v>
       </c>
       <c r="R65" t="n">
-        <v>6939547</v>
+        <v>6939333</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7905,7 +7893,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7927,10 +7915,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120215676</v>
+        <v>120215712</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7943,34 +7931,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555303</v>
+        <v>555317</v>
       </c>
       <c r="R66" t="n">
-        <v>6939259</v>
+        <v>6939671</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8016,7 +8004,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8038,10 +8026,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120215670</v>
+        <v>120215672</v>
       </c>
       <c r="B67" t="n">
-        <v>91850</v>
+        <v>90084</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8050,25 +8038,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>256703</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8078,10 +8066,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555366</v>
+        <v>555256</v>
       </c>
       <c r="R67" t="n">
-        <v>6939325</v>
+        <v>6939301</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8149,10 +8137,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120215677</v>
+        <v>120215686</v>
       </c>
       <c r="B68" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8165,21 +8153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8189,10 +8177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555282</v>
+        <v>555296</v>
       </c>
       <c r="R68" t="n">
-        <v>6939236</v>
+        <v>6939306</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8238,7 +8226,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8260,7 +8248,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120215725</v>
+        <v>120215730</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -8300,10 +8288,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555442</v>
+        <v>555499</v>
       </c>
       <c r="R69" t="n">
-        <v>6939660</v>
+        <v>6939547</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8349,7 +8337,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8371,10 +8359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120215667</v>
+        <v>120215735</v>
       </c>
       <c r="B70" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8383,38 +8371,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555412</v>
+        <v>555516</v>
       </c>
       <c r="R70" t="n">
-        <v>6939333</v>
+        <v>6939844</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8460,7 +8448,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskogssvacka</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8482,7 +8470,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120215693</v>
+        <v>120215673</v>
       </c>
       <c r="B71" t="n">
         <v>91850</v>
@@ -8522,10 +8510,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555255</v>
+        <v>555256</v>
       </c>
       <c r="R71" t="n">
-        <v>6939329</v>
+        <v>6939303</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8571,7 +8559,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8593,10 +8581,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120215722</v>
+        <v>120215723</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8605,38 +8593,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555358</v>
+        <v>555369</v>
       </c>
       <c r="R72" t="n">
-        <v>6939668</v>
+        <v>6939717</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8682,7 +8674,15 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>gles 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga med rotbenen kvar</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120215663</v>
+        <v>120215721</v>
       </c>
       <c r="B73" t="n">
-        <v>91870</v>
+        <v>78279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8716,38 +8716,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555335</v>
+        <v>555389</v>
       </c>
       <c r="R73" t="n">
-        <v>6939295</v>
+        <v>6939706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8793,7 +8793,15 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8815,10 +8823,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120215674</v>
+        <v>120215691</v>
       </c>
       <c r="B74" t="n">
-        <v>91042</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8827,25 +8835,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5467</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8855,10 +8863,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555331</v>
+        <v>555287</v>
       </c>
       <c r="R74" t="n">
-        <v>6939284</v>
+        <v>6939378</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8904,15 +8912,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i sydostvänd nipa</t>
-        </is>
-      </c>
-      <c r="AN74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga av fallen högstubbe, kollat med lutreaktion</t>
+          <t>140-årig sandtallskog med lingon och lav i sydslänt</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8934,7 +8934,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120215673</v>
+        <v>120215693</v>
       </c>
       <c r="B75" t="n">
         <v>91850</v>
@@ -8974,10 +8974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555256</v>
+        <v>555255</v>
       </c>
       <c r="R75" t="n">
-        <v>6939303</v>
+        <v>6939329</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>140-årig sandtallskog med lingon och väggmossa i nederkant av sydslänt</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120215705</v>
+        <v>120215704</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9057,25 +9057,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555220</v>
+        <v>555333</v>
       </c>
       <c r="R76" t="n">
-        <v>6939479</v>
+        <v>6939465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog i lavrik sydvänd slänt med inslag av ganska gammal tall</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120215710</v>
+        <v>120215671</v>
       </c>
       <c r="B77" t="n">
-        <v>89247</v>
+        <v>91874</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9168,38 +9168,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1596</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555308</v>
+        <v>555366</v>
       </c>
       <c r="R77" t="n">
-        <v>6939650</v>
+        <v>6939325</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i nederdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9267,10 +9267,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120215680</v>
+        <v>120215675</v>
       </c>
       <c r="B78" t="n">
-        <v>90545</v>
+        <v>92048</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9279,25 +9279,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555303</v>
+        <v>555371</v>
       </c>
       <c r="R78" t="n">
-        <v>6939247</v>
+        <v>6939272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9356,12 +9356,15 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
-        </is>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN78" t="n">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>gammal tallågerest medkolade ytor</t>
+          <t>1 substratenheter # gammal tallåga efter törskatetall</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9383,10 +9386,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120215712</v>
+        <v>120215714</v>
       </c>
       <c r="B79" t="n">
-        <v>90084</v>
+        <v>78187</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9395,25 +9398,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>256703</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9423,10 +9426,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555317</v>
+        <v>555320</v>
       </c>
       <c r="R79" t="n">
-        <v>6939671</v>
+        <v>6939663</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9473,6 +9476,14 @@
       <c r="AI79" t="inlineStr">
         <is>
           <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallågerest</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9494,10 +9505,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120215738</v>
+        <v>120215711</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9506,25 +9517,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9534,10 +9545,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555480</v>
+        <v>555311</v>
       </c>
       <c r="R80" t="n">
-        <v>6939802</v>
+        <v>6939662</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9583,7 +9594,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>under gammal tallågerest</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9605,10 +9621,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215717</v>
+        <v>120215715</v>
       </c>
       <c r="B81" t="n">
-        <v>78279</v>
+        <v>91328</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9617,25 +9633,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9645,10 +9661,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555370</v>
+        <v>555320</v>
       </c>
       <c r="R81" t="n">
-        <v>6939656</v>
+        <v>6939665</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9694,15 +9710,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AN81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9724,10 +9732,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215684</v>
+        <v>120215663</v>
       </c>
       <c r="B82" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9740,21 +9748,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9764,10 +9772,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555328</v>
+        <v>555335</v>
       </c>
       <c r="R82" t="n">
-        <v>6939359</v>
+        <v>6939295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9813,7 +9821,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9835,10 +9843,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120215671</v>
+        <v>120215717</v>
       </c>
       <c r="B83" t="n">
-        <v>91874</v>
+        <v>78279</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9851,34 +9859,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555366</v>
+        <v>555370</v>
       </c>
       <c r="R83" t="n">
-        <v>6939325</v>
+        <v>6939656</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9924,7 +9932,15 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9946,7 +9962,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120215735</v>
+        <v>120215719</v>
       </c>
       <c r="B84" t="n">
         <v>91858</v>
@@ -9986,10 +10002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555516</v>
+        <v>555393</v>
       </c>
       <c r="R84" t="n">
-        <v>6939844</v>
+        <v>6939610</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10035,7 +10051,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10057,7 +10073,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120215733</v>
+        <v>120215743</v>
       </c>
       <c r="B85" t="n">
         <v>91858</v>
@@ -10097,10 +10113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555508</v>
+        <v>555438</v>
       </c>
       <c r="R85" t="n">
-        <v>6939693</v>
+        <v>6939819</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10146,7 +10162,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskogssluttning</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10168,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120215714</v>
+        <v>120215670</v>
       </c>
       <c r="B86" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10184,34 +10200,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555320</v>
+        <v>555366</v>
       </c>
       <c r="R86" t="n">
-        <v>6939663</v>
+        <v>6939325</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10257,15 +10273,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
-        </is>
-      </c>
-      <c r="AN86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallågerest</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10287,10 +10295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120215665</v>
+        <v>120215703</v>
       </c>
       <c r="B87" t="n">
-        <v>90416</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10299,25 +10307,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6020</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10327,10 +10335,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555444</v>
+        <v>555338</v>
       </c>
       <c r="R87" t="n">
-        <v>6939356</v>
+        <v>6939447</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10376,15 +10384,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120215729</v>
+        <v>120215709</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555492</v>
+        <v>555350</v>
       </c>
       <c r="R15" t="n">
-        <v>6939553</v>
+        <v>6939568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,15 +2272,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal tallåga</t>
+          <t>150-årig sandtallskog med lavfläckar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2302,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120215709</v>
+        <v>120215729</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555350</v>
+        <v>555492</v>
       </c>
       <c r="R16" t="n">
-        <v>6939568</v>
+        <v>6939553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,7 +2383,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med lavfläckar</t>
+          <t>150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal tallåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120215736</v>
+        <v>120215668</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3222,34 +3222,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555530</v>
+        <v>555394</v>
       </c>
       <c r="R24" t="n">
-        <v>6939888</v>
+        <v>6939336</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3295,7 +3295,15 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3317,10 +3325,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120215668</v>
+        <v>120215736</v>
       </c>
       <c r="B25" t="n">
-        <v>79527</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3333,34 +3341,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555394</v>
+        <v>555530</v>
       </c>
       <c r="R25" t="n">
-        <v>6939336</v>
+        <v>6939888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,15 +3414,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
-        </is>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120215726</v>
+        <v>120215682</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,34 +3452,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555445</v>
+        <v>555325</v>
       </c>
       <c r="R26" t="n">
-        <v>6939653</v>
+        <v>6939312</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
+          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120215682</v>
+        <v>120215726</v>
       </c>
       <c r="B27" t="n">
-        <v>91874</v>
+        <v>91881</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,34 +3563,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555325</v>
+        <v>555445</v>
       </c>
       <c r="R27" t="n">
-        <v>6939312</v>
+        <v>6939653</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lav i västslänt</t>
+          <t>i körspår i 150-årig sandtallskog med lavfläckar och spridda äldre tallar</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120215688</v>
+        <v>120215706</v>
       </c>
       <c r="B52" t="n">
-        <v>90848</v>
+        <v>91481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6365,38 +6365,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>71</v>
+        <v>4745</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555246</v>
+        <v>555195</v>
       </c>
       <c r="R52" t="n">
-        <v>6939300</v>
+        <v>6939463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6442,15 +6442,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
-        </is>
-      </c>
-      <c r="AN52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6472,10 +6464,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120215706</v>
+        <v>120215738</v>
       </c>
       <c r="B53" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6484,38 +6476,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S om Lokarna, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555195</v>
+        <v>555480</v>
       </c>
       <c r="R53" t="n">
-        <v>6939463</v>
+        <v>6939802</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6561,7 +6553,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6583,10 +6575,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120215738</v>
+        <v>120215688</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>90848</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6595,38 +6587,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555480</v>
+        <v>555246</v>
       </c>
       <c r="R54" t="n">
-        <v>6939802</v>
+        <v>6939300</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6672,7 +6664,15 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig sandtallskogssvacka med spridda ännu äldre tallar</t>
+          <t>140-årig gles sandtallskog i lavrik terrängsvacka med graninslag</t>
+        </is>
+      </c>
+      <c r="AN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på kolad ved under fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6805,10 +6805,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120215731</v>
+        <v>120215677</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6821,34 +6821,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555532</v>
+        <v>555282</v>
       </c>
       <c r="R56" t="n">
-        <v>6939560</v>
+        <v>6939236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
+          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120215664</v>
+        <v>120215731</v>
       </c>
       <c r="B57" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6928,38 +6928,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555450</v>
+        <v>555532</v>
       </c>
       <c r="R57" t="n">
-        <v>6939355</v>
+        <v>6939560</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog med tjocka moss- och rismattor</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120215677</v>
+        <v>120215664</v>
       </c>
       <c r="B58" t="n">
-        <v>90084</v>
+        <v>91850</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7039,25 +7039,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555282</v>
+        <v>555450</v>
       </c>
       <c r="R58" t="n">
-        <v>6939236</v>
+        <v>6939355</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och gråal i rikare nipa</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120215697</v>
+        <v>120215667</v>
       </c>
       <c r="B59" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7150,25 +7150,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555218</v>
+        <v>555412</v>
       </c>
       <c r="R59" t="n">
-        <v>6939369</v>
+        <v>6939333</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog med lingon och lavfläckar</t>
+          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7249,10 +7249,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120215667</v>
+        <v>120215713</v>
       </c>
       <c r="B60" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7261,38 +7261,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555412</v>
+        <v>555307</v>
       </c>
       <c r="R60" t="n">
-        <v>6939333</v>
+        <v>6939679</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog med inslag av gran och asp i rikare nipa</t>
+          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120215713</v>
+        <v>120215697</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7372,38 +7372,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555307</v>
+        <v>555218</v>
       </c>
       <c r="R61" t="n">
-        <v>6939679</v>
+        <v>6939369</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med högt bärris</t>
+          <t>140-årig sandtallskog med lingon och lavfläckar</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120215715</v>
+        <v>120215663</v>
       </c>
       <c r="B81" t="n">
-        <v>91328</v>
+        <v>91870</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9633,38 +9633,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>4366</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, S grustag, Mpd</t>
+          <t>NO om Vargtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555320</v>
+        <v>555335</v>
       </c>
       <c r="R81" t="n">
-        <v>6939665</v>
+        <v>6939295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
+          <t>150-årig sandtallskog på sandig getrygg</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9732,10 +9732,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120215663</v>
+        <v>120215715</v>
       </c>
       <c r="B82" t="n">
-        <v>91870</v>
+        <v>91328</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,38 +9744,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4366</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NO om Vargtjärn, Mpd</t>
+          <t>NO om Vargtjärn, S grustag, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555335</v>
+        <v>555320</v>
       </c>
       <c r="R82" t="n">
-        <v>6939295</v>
+        <v>6939665</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog på sandig getrygg</t>
+          <t>150-årig sandtallskog i överdel av sluttning med spridd gammal tall, på lavmark</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 43968-2023 artfynd.xlsx
+++ b/artfynd/A 43968-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215688</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215714</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215704</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215715</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013418</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013426</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013429</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215671</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1840,6 +1895,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215682</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215683</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215675</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215664</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215667</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215670</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215673</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2696,6 +2791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215679</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215693</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2913,6 +3018,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215728</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3014,6 +3124,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013415</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3115,6 +3230,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013417</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3216,6 +3336,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013427</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3317,6 +3442,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013439</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3418,6 +3548,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013467</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3519,6 +3654,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013470</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3620,6 +3760,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013472</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3726,6 +3871,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215669</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3832,6 +3982,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215676</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3938,6 +4093,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215678</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4044,6 +4204,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215684</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4150,6 +4315,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215686</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4256,6 +4426,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215691</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4362,6 +4537,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215694</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4468,6 +4648,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215696</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4574,6 +4759,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215702</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4680,6 +4870,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215703</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4786,6 +4981,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215705</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4892,6 +5092,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215707</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4998,6 +5203,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215708</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5104,6 +5314,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215709</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5210,6 +5425,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215713</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5316,6 +5536,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215719</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5422,6 +5647,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215720</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5528,6 +5758,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215722</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5634,6 +5869,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215724</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5740,6 +5980,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215725</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5846,6 +6091,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215727</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5952,6 +6202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215730</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6058,6 +6313,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215731</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6164,6 +6424,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215732</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6270,6 +6535,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215733</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6376,6 +6646,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215735</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6482,6 +6757,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215736</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6588,6 +6868,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215738</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6694,6 +6979,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215743</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6800,6 +7090,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215662</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6906,6 +7201,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215663</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7012,6 +7312,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215695</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7113,6 +7418,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013469</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7214,6 +7524,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013471</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7320,6 +7635,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215706</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7431,6 +7751,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215680</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7537,6 +7862,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215690</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7651,6 +7981,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215674</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7757,6 +8092,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215726</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7871,6 +8211,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215665</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7985,6 +8330,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215666</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8103,6 +8453,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215723</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8209,6 +8564,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215692</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8315,6 +8675,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215697</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8421,6 +8786,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215740</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8522,6 +8892,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013424</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8623,6 +8998,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013428</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8724,6 +9104,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013425</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8825,6 +9210,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013430</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8926,6 +9316,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102510752</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9037,6 +9432,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215681</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9151,6 +9551,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215729</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9265,6 +9670,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215668</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9366,6 +9776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102510769</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9467,6 +9882,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466261</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9568,6 +9988,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466262</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9669,6 +10094,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466272</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9770,6 +10200,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466273</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9871,6 +10306,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466299</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9977,6 +10417,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466695</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10078,6 +10523,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96013431</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10192,6 +10642,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215687</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10306,6 +10761,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215717</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10420,6 +10880,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215721</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10531,6 +10996,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215711</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10637,6 +11107,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215672</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10743,6 +11218,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215677</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10849,6 +11329,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215712</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10955,8 +11440,112 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215742</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>